--- a/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
+++ b/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
@@ -8,9 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="加法探针_全实验总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="迷宫导航_纯RL实验总表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="加法_层数L扫描" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="加法_宽度d扫描" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="迷宫导航_全实验总表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,14 +663,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>加法算术探针全实验矩阵 (专属独立板块)</t>
+          <t>TinyGPT 加法算术探针全量实验总表 (单表全景矩阵)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>收录全部加法架构扫描、CoT vs Plain、自问自答RL与INT8量化实验</t>
+          <t>共 124 项实验统一按序号 001..124 顺序排列</t>
         </is>
       </c>
     </row>
@@ -689,7 +687,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>实验标识/具体配置</t>
+          <t>实验描述与具体配置</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -924,14 +922,14 @@
       </c>
       <c r="AX3" s="8" t="inlineStr">
         <is>
-          <t>加法算术实验实测记载</t>
+          <t>实测现象与表现记载</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>NLAY-01</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -1167,7 +1165,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>NLAY-02</t>
+          <t>002</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -1403,7 +1401,7 @@
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>NLAY-03</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -1639,7 +1637,7 @@
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>NLAY-04</t>
+          <t>004</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -1875,7 +1873,7 @@
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>NLAY-05</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -2111,7 +2109,7 @@
     <row r="9" ht="24" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>NLAY-06</t>
+          <t>006</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -2347,7 +2345,7 @@
     <row r="10" ht="24" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>NLAY-07</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -2583,7 +2581,7 @@
     <row r="11" ht="24" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>NLAY-08</t>
+          <t>008</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -2819,7 +2817,7 @@
     <row r="12" ht="24" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>NLAY-09</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -3055,7 +3053,7 @@
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>NLAY-10</t>
+          <t>010</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -3291,7 +3289,7 @@
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>NEMBD-01</t>
+          <t>011</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -3527,7 +3525,7 @@
     <row r="15" ht="24" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>NEMBD-02</t>
+          <t>012</t>
         </is>
       </c>
       <c r="B15" s="20" t="inlineStr">
@@ -3763,7 +3761,7 @@
     <row r="16" ht="24" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>NEMBD-03</t>
+          <t>013</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -3999,7 +3997,7 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>NEMBD-04</t>
+          <t>014</t>
         </is>
       </c>
       <c r="B17" s="20" t="inlineStr">
@@ -4235,7 +4233,7 @@
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>NEMBD-05</t>
+          <t>015</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -4471,7 +4469,7 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>NEMBD-06</t>
+          <t>016</t>
         </is>
       </c>
       <c r="B19" s="20" t="inlineStr">
@@ -4707,7 +4705,7 @@
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>NEMBD-07</t>
+          <t>017</t>
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -4943,7 +4941,7 @@
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>NEMBD-08</t>
+          <t>018</t>
         </is>
       </c>
       <c r="B21" s="20" t="inlineStr">
@@ -5179,7 +5177,7 @@
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>NEMBD-09</t>
+          <t>019</t>
         </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -5415,7 +5413,7 @@
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>NEMBD-10</t>
+          <t>020</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr">
@@ -5651,7 +5649,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>NEMBD-11</t>
+          <t>021</t>
         </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -5887,7 +5885,7 @@
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>NEMBD-12</t>
+          <t>022</t>
         </is>
       </c>
       <c r="B25" s="20" t="inlineStr">
@@ -6123,7 +6121,7 @@
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>NEMBD-13</t>
+          <t>023</t>
         </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -6359,7 +6357,7 @@
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>NEMBD-14</t>
+          <t>024</t>
         </is>
       </c>
       <c r="B27" s="20" t="inlineStr">
@@ -6595,7 +6593,7 @@
     <row r="28" ht="24" customHeight="1">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>NEMBD-15</t>
+          <t>025</t>
         </is>
       </c>
       <c r="B28" s="10" t="inlineStr">
@@ -6831,7 +6829,7 @@
     <row r="29" ht="24" customHeight="1">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>NEMBD-16</t>
+          <t>026</t>
         </is>
       </c>
       <c r="B29" s="20" t="inlineStr">
@@ -7067,7 +7065,7 @@
     <row r="30" ht="24" customHeight="1">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>NHEAD-01</t>
+          <t>027</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -7303,7 +7301,7 @@
     <row r="31" ht="24" customHeight="1">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>NHEAD-02</t>
+          <t>028</t>
         </is>
       </c>
       <c r="B31" s="20" t="inlineStr">
@@ -7539,7 +7537,7 @@
     <row r="32" ht="24" customHeight="1">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>NHEAD-03</t>
+          <t>029</t>
         </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -7775,7 +7773,7 @@
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>NHEAD-04</t>
+          <t>030</t>
         </is>
       </c>
       <c r="B33" s="20" t="inlineStr">
@@ -8011,7 +8009,7 @@
     <row r="34" ht="24" customHeight="1">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>NHEAD-05</t>
+          <t>031</t>
         </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -8247,7 +8245,7 @@
     <row r="35" ht="24" customHeight="1">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>NHEAD-06</t>
+          <t>032</t>
         </is>
       </c>
       <c r="B35" s="20" t="inlineStr">
@@ -8483,7 +8481,7 @@
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>NHEAD-07</t>
+          <t>033</t>
         </is>
       </c>
       <c r="B36" s="10" t="inlineStr">
@@ -8719,7 +8717,7 @@
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>NHEAD-08</t>
+          <t>034</t>
         </is>
       </c>
       <c r="B37" s="20" t="inlineStr">
@@ -8955,7 +8953,7 @@
     <row r="38" ht="24" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>DP-01</t>
+          <t>035</t>
         </is>
       </c>
       <c r="B38" s="10" t="inlineStr">
@@ -9191,7 +9189,7 @@
     <row r="39" ht="24" customHeight="1">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>DP-02</t>
+          <t>036</t>
         </is>
       </c>
       <c r="B39" s="20" t="inlineStr">
@@ -9427,7 +9425,7 @@
     <row r="40" ht="24" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>DP-03</t>
+          <t>037</t>
         </is>
       </c>
       <c r="B40" s="10" t="inlineStr">
@@ -9663,7 +9661,7 @@
     <row r="41" ht="24" customHeight="1">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>DP-04</t>
+          <t>038</t>
         </is>
       </c>
       <c r="B41" s="20" t="inlineStr">
@@ -9899,7 +9897,7 @@
     <row r="42" ht="24" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>DP-05</t>
+          <t>039</t>
         </is>
       </c>
       <c r="B42" s="10" t="inlineStr">
@@ -10135,7 +10133,7 @@
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>ATTN-01</t>
+          <t>040</t>
         </is>
       </c>
       <c r="B43" s="20" t="inlineStr">
@@ -10371,7 +10369,7 @@
     <row r="44" ht="24" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>ATTN-02</t>
+          <t>041</t>
         </is>
       </c>
       <c r="B44" s="10" t="inlineStr">
@@ -10607,7 +10605,7 @@
     <row r="45" ht="24" customHeight="1">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>ATTN-03</t>
+          <t>042</t>
         </is>
       </c>
       <c r="B45" s="20" t="inlineStr">
@@ -10843,7 +10841,7 @@
     <row r="46" ht="24" customHeight="1">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>ATTN-04</t>
+          <t>043</t>
         </is>
       </c>
       <c r="B46" s="10" t="inlineStr">
@@ -11079,7 +11077,7 @@
     <row r="47" ht="24" customHeight="1">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>ATTN-05</t>
+          <t>044</t>
         </is>
       </c>
       <c r="B47" s="20" t="inlineStr">
@@ -11315,7 +11313,7 @@
     <row r="48" ht="24" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>ATTN-06</t>
+          <t>045</t>
         </is>
       </c>
       <c r="B48" s="10" t="inlineStr">
@@ -11551,7 +11549,7 @@
     <row r="49" ht="24" customHeight="1">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>ATTN-07</t>
+          <t>046</t>
         </is>
       </c>
       <c r="B49" s="20" t="inlineStr">
@@ -11787,7 +11785,7 @@
     <row r="50" ht="24" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>MOE-EXP-01</t>
+          <t>047</t>
         </is>
       </c>
       <c r="B50" s="10" t="inlineStr">
@@ -12023,7 +12021,7 @@
     <row r="51" ht="24" customHeight="1">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>MOE-EXP-02</t>
+          <t>048</t>
         </is>
       </c>
       <c r="B51" s="20" t="inlineStr">
@@ -12259,7 +12257,7 @@
     <row r="52" ht="24" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>MOE-EXP-03</t>
+          <t>049</t>
         </is>
       </c>
       <c r="B52" s="10" t="inlineStr">
@@ -12495,7 +12493,7 @@
     <row r="53" ht="24" customHeight="1">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>MOE-EXP-04</t>
+          <t>050</t>
         </is>
       </c>
       <c r="B53" s="20" t="inlineStr">
@@ -12731,7 +12729,7 @@
     <row r="54" ht="24" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>MOE-EXP-05</t>
+          <t>051</t>
         </is>
       </c>
       <c r="B54" s="10" t="inlineStr">
@@ -12967,7 +12965,7 @@
     <row r="55" ht="24" customHeight="1">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>MOE-TOPK-01</t>
+          <t>052</t>
         </is>
       </c>
       <c r="B55" s="20" t="inlineStr">
@@ -13203,7 +13201,7 @@
     <row r="56" ht="24" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>MOE-TOPK-02</t>
+          <t>053</t>
         </is>
       </c>
       <c r="B56" s="10" t="inlineStr">
@@ -13439,7 +13437,7 @@
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>MOE-TOPK-03</t>
+          <t>054</t>
         </is>
       </c>
       <c r="B57" s="20" t="inlineStr">
@@ -13675,7 +13673,7 @@
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>MOE-AUX-01</t>
+          <t>055</t>
         </is>
       </c>
       <c r="B58" s="10" t="inlineStr">
@@ -13911,7 +13909,7 @@
     <row r="59" ht="24" customHeight="1">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>MOE-AUX-02</t>
+          <t>056</t>
         </is>
       </c>
       <c r="B59" s="20" t="inlineStr">
@@ -14147,7 +14145,7 @@
     <row r="60" ht="24" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>MOE-AUX-03</t>
+          <t>057</t>
         </is>
       </c>
       <c r="B60" s="10" t="inlineStr">
@@ -14383,7 +14381,7 @@
     <row r="61" ht="24" customHeight="1">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>MOE-AUX-04</t>
+          <t>058</t>
         </is>
       </c>
       <c r="B61" s="20" t="inlineStr">
@@ -14619,7 +14617,7 @@
     <row r="62" ht="24" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>MOE-AUX-05</t>
+          <t>059</t>
         </is>
       </c>
       <c r="B62" s="10" t="inlineStr">
@@ -14855,7 +14853,7 @@
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>BN-DIM-01</t>
+          <t>060</t>
         </is>
       </c>
       <c r="B63" s="20" t="inlineStr">
@@ -15091,7 +15089,7 @@
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>BN-DIM-02</t>
+          <t>061</t>
         </is>
       </c>
       <c r="B64" s="10" t="inlineStr">
@@ -15327,7 +15325,7 @@
     <row r="65" ht="24" customHeight="1">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>BN-DIM-03</t>
+          <t>062</t>
         </is>
       </c>
       <c r="B65" s="20" t="inlineStr">
@@ -15563,7 +15561,7 @@
     <row r="66" ht="24" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>BN-DIM-04</t>
+          <t>063</t>
         </is>
       </c>
       <c r="B66" s="10" t="inlineStr">
@@ -15799,7 +15797,7 @@
     <row r="67" ht="24" customHeight="1">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>BN-POS-01</t>
+          <t>064</t>
         </is>
       </c>
       <c r="B67" s="20" t="inlineStr">
@@ -16035,7 +16033,7 @@
     <row r="68" ht="24" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>BN-POS-02</t>
+          <t>065</t>
         </is>
       </c>
       <c r="B68" s="10" t="inlineStr">
@@ -16271,7 +16269,7 @@
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>BN-POS-03</t>
+          <t>066</t>
         </is>
       </c>
       <c r="B69" s="20" t="inlineStr">
@@ -16507,7 +16505,7 @@
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>BN-POS-04</t>
+          <t>067</t>
         </is>
       </c>
       <c r="B70" s="10" t="inlineStr">
@@ -16743,7 +16741,7 @@
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="19" t="inlineStr">
         <is>
-          <t>BN-POS-05</t>
+          <t>068</t>
         </is>
       </c>
       <c r="B71" s="20" t="inlineStr">
@@ -16979,7 +16977,7 @@
     <row r="72" ht="24" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>PLAIN-01</t>
+          <t>069</t>
         </is>
       </c>
       <c r="B72" s="10" t="inlineStr">
@@ -17215,7 +17213,7 @@
     <row r="73" ht="24" customHeight="1">
       <c r="A73" s="19" t="inlineStr">
         <is>
-          <t>PLAIN-02</t>
+          <t>070</t>
         </is>
       </c>
       <c r="B73" s="20" t="inlineStr">
@@ -17451,7 +17449,7 @@
     <row r="74" ht="24" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>PLAIN-03</t>
+          <t>071</t>
         </is>
       </c>
       <c r="B74" s="10" t="inlineStr">
@@ -17687,7 +17685,7 @@
     <row r="75" ht="24" customHeight="1">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>PLAIN-04</t>
+          <t>072</t>
         </is>
       </c>
       <c r="B75" s="20" t="inlineStr">
@@ -17923,7 +17921,7 @@
     <row r="76" ht="24" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>PLAIN-05</t>
+          <t>073</t>
         </is>
       </c>
       <c r="B76" s="10" t="inlineStr">
@@ -18159,7 +18157,7 @@
     <row r="77" ht="24" customHeight="1">
       <c r="A77" s="19" t="inlineStr">
         <is>
-          <t>PLAIN-06</t>
+          <t>074</t>
         </is>
       </c>
       <c r="B77" s="20" t="inlineStr">
@@ -18395,7 +18393,7 @@
     <row r="78" ht="24" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>PLAIN-07</t>
+          <t>075</t>
         </is>
       </c>
       <c r="B78" s="10" t="inlineStr">
@@ -18631,7 +18629,7 @@
     <row r="79" ht="24" customHeight="1">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>PLAIN-08</t>
+          <t>076</t>
         </is>
       </c>
       <c r="B79" s="20" t="inlineStr">
@@ -18867,7 +18865,7 @@
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>PLAIN-09</t>
+          <t>077</t>
         </is>
       </c>
       <c r="B80" s="10" t="inlineStr">
@@ -19103,7 +19101,7 @@
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="19" t="inlineStr">
         <is>
-          <t>COT-01</t>
+          <t>078</t>
         </is>
       </c>
       <c r="B81" s="20" t="inlineStr">
@@ -19339,7 +19337,7 @@
     <row r="82" ht="24" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>COT-02</t>
+          <t>079</t>
         </is>
       </c>
       <c r="B82" s="10" t="inlineStr">
@@ -19575,7 +19573,7 @@
     <row r="83" ht="24" customHeight="1">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>COT-03</t>
+          <t>080</t>
         </is>
       </c>
       <c r="B83" s="20" t="inlineStr">
@@ -19811,7 +19809,7 @@
     <row r="84" ht="24" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>COT-04</t>
+          <t>081</t>
         </is>
       </c>
       <c r="B84" s="10" t="inlineStr">
@@ -20047,7 +20045,7 @@
     <row r="85" ht="24" customHeight="1">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>COT-05</t>
+          <t>082</t>
         </is>
       </c>
       <c r="B85" s="20" t="inlineStr">
@@ -20283,7 +20281,7 @@
     <row r="86" ht="24" customHeight="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>COT-06</t>
+          <t>083</t>
         </is>
       </c>
       <c r="B86" s="10" t="inlineStr">
@@ -20519,7 +20517,7 @@
     <row r="87" ht="24" customHeight="1">
       <c r="A87" s="19" t="inlineStr">
         <is>
-          <t>COT-07</t>
+          <t>084</t>
         </is>
       </c>
       <c r="B87" s="20" t="inlineStr">
@@ -20755,7 +20753,7 @@
     <row r="88" ht="24" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>COT-08</t>
+          <t>085</t>
         </is>
       </c>
       <c r="B88" s="10" t="inlineStr">
@@ -20991,7 +20989,7 @@
     <row r="89" ht="24" customHeight="1">
       <c r="A89" s="19" t="inlineStr">
         <is>
-          <t>COT-09</t>
+          <t>086</t>
         </is>
       </c>
       <c r="B89" s="20" t="inlineStr">
@@ -21227,7 +21225,7 @@
     <row r="90" ht="24" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>STEP-l2_d64-500</t>
+          <t>087</t>
         </is>
       </c>
       <c r="B90" s="10" t="inlineStr">
@@ -21463,7 +21461,7 @@
     <row r="91" ht="24" customHeight="1">
       <c r="A91" s="19" t="inlineStr">
         <is>
-          <t>STEP-l2_d64-1000</t>
+          <t>088</t>
         </is>
       </c>
       <c r="B91" s="20" t="inlineStr">
@@ -21699,7 +21697,7 @@
     <row r="92" ht="24" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>STEP-l2_d64-2000</t>
+          <t>089</t>
         </is>
       </c>
       <c r="B92" s="10" t="inlineStr">
@@ -21935,7 +21933,7 @@
     <row r="93" ht="24" customHeight="1">
       <c r="A93" s="19" t="inlineStr">
         <is>
-          <t>STEP-l2_d64-4000</t>
+          <t>090</t>
         </is>
       </c>
       <c r="B93" s="20" t="inlineStr">
@@ -22171,7 +22169,7 @@
     <row r="94" ht="24" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>STEP-l2_d64-500</t>
+          <t>091</t>
         </is>
       </c>
       <c r="B94" s="10" t="inlineStr">
@@ -22407,7 +22405,7 @@
     <row r="95" ht="24" customHeight="1">
       <c r="A95" s="19" t="inlineStr">
         <is>
-          <t>STEP-l2_d64-1000</t>
+          <t>092</t>
         </is>
       </c>
       <c r="B95" s="20" t="inlineStr">
@@ -22643,7 +22641,7 @@
     <row r="96" ht="24" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>STEP-l2_d64-2000</t>
+          <t>093</t>
         </is>
       </c>
       <c r="B96" s="10" t="inlineStr">
@@ -22879,7 +22877,7 @@
     <row r="97" ht="24" customHeight="1">
       <c r="A97" s="19" t="inlineStr">
         <is>
-          <t>STEP-l2_d64-4000</t>
+          <t>094</t>
         </is>
       </c>
       <c r="B97" s="20" t="inlineStr">
@@ -23115,7 +23113,7 @@
     <row r="98" ht="24" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-500</t>
+          <t>095</t>
         </is>
       </c>
       <c r="B98" s="10" t="inlineStr">
@@ -23351,7 +23349,7 @@
     <row r="99" ht="24" customHeight="1">
       <c r="A99" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-1000</t>
+          <t>096</t>
         </is>
       </c>
       <c r="B99" s="20" t="inlineStr">
@@ -23587,7 +23585,7 @@
     <row r="100" ht="24" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-2000</t>
+          <t>097</t>
         </is>
       </c>
       <c r="B100" s="10" t="inlineStr">
@@ -23823,7 +23821,7 @@
     <row r="101" ht="24" customHeight="1">
       <c r="A101" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-4000</t>
+          <t>098</t>
         </is>
       </c>
       <c r="B101" s="20" t="inlineStr">
@@ -24059,7 +24057,7 @@
     <row r="102" ht="24" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-500</t>
+          <t>099</t>
         </is>
       </c>
       <c r="B102" s="10" t="inlineStr">
@@ -24295,7 +24293,7 @@
     <row r="103" ht="24" customHeight="1">
       <c r="A103" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-1000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="B103" s="20" t="inlineStr">
@@ -24531,7 +24529,7 @@
     <row r="104" ht="24" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-2000</t>
+          <t>101</t>
         </is>
       </c>
       <c r="B104" s="10" t="inlineStr">
@@ -24767,7 +24765,7 @@
     <row r="105" ht="24" customHeight="1">
       <c r="A105" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-4000</t>
+          <t>102</t>
         </is>
       </c>
       <c r="B105" s="20" t="inlineStr">
@@ -25003,7 +25001,7 @@
     <row r="106" ht="24" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-500</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B106" s="10" t="inlineStr">
@@ -25239,7 +25237,7 @@
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-1000</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B107" s="20" t="inlineStr">
@@ -25475,7 +25473,7 @@
     <row r="108" ht="24" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-2000</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B108" s="10" t="inlineStr">
@@ -25711,7 +25709,7 @@
     <row r="109" ht="24" customHeight="1">
       <c r="A109" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-4000</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B109" s="20" t="inlineStr">
@@ -25947,7 +25945,7 @@
     <row r="110" ht="24" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-500</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B110" s="10" t="inlineStr">
@@ -26183,7 +26181,7 @@
     <row r="111" ht="24" customHeight="1">
       <c r="A111" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-1000</t>
+          <t>108</t>
         </is>
       </c>
       <c r="B111" s="20" t="inlineStr">
@@ -26419,7 +26417,7 @@
     <row r="112" ht="24" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-2000</t>
+          <t>109</t>
         </is>
       </c>
       <c r="B112" s="10" t="inlineStr">
@@ -26655,7 +26653,7 @@
     <row r="113" ht="24" customHeight="1">
       <c r="A113" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-4000</t>
+          <t>110</t>
         </is>
       </c>
       <c r="B113" s="20" t="inlineStr">
@@ -26891,7 +26889,7 @@
     <row r="114" ht="24" customHeight="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-500</t>
+          <t>111</t>
         </is>
       </c>
       <c r="B114" s="10" t="inlineStr">
@@ -27127,7 +27125,7 @@
     <row r="115" ht="24" customHeight="1">
       <c r="A115" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-1000</t>
+          <t>112</t>
         </is>
       </c>
       <c r="B115" s="20" t="inlineStr">
@@ -27363,7 +27361,7 @@
     <row r="116" ht="24" customHeight="1">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-2000</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B116" s="10" t="inlineStr">
@@ -27599,7 +27597,7 @@
     <row r="117" ht="24" customHeight="1">
       <c r="A117" s="19" t="inlineStr">
         <is>
-          <t>STEP-l4_d12-4000</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B117" s="20" t="inlineStr">
@@ -27835,7 +27833,7 @@
     <row r="118" ht="24" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>RL-NAIVE</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B118" s="10" t="inlineStr">
@@ -28071,7 +28069,7 @@
     <row r="119" ht="24" customHeight="1">
       <c r="A119" s="19" t="inlineStr">
         <is>
-          <t>RL-ANCHOR2</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B119" s="20" t="inlineStr">
@@ -28307,7 +28305,7 @@
     <row r="120" ht="24" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>RL-MEM-0.5</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B120" s="10" t="inlineStr">
@@ -28543,7 +28541,7 @@
     <row r="121" ht="24" customHeight="1">
       <c r="A121" s="19" t="inlineStr">
         <is>
-          <t>RL-MEM-1.0</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B121" s="20" t="inlineStr">
@@ -28779,7 +28777,7 @@
     <row r="122" ht="24" customHeight="1">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>RL-MEM-1.5</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B122" s="10" t="inlineStr">
@@ -29015,7 +29013,7 @@
     <row r="123" ht="24" customHeight="1">
       <c r="A123" s="19" t="inlineStr">
         <is>
-          <t>RL-MEM-2.0</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B123" s="20" t="inlineStr">
@@ -29251,7 +29249,7 @@
     <row r="124" ht="24" customHeight="1">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>RL-LRU-WIN</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B124" s="10" t="inlineStr">
@@ -29487,7 +29485,7 @@
     <row r="125" ht="24" customHeight="1">
       <c r="A125" s="19" t="inlineStr">
         <is>
-          <t>RL-TF-0.25</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B125" s="20" t="inlineStr">
@@ -29723,7 +29721,7 @@
     <row r="126" ht="24" customHeight="1">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>RL-TF-0.50</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B126" s="10" t="inlineStr">
@@ -29959,7 +29957,7 @@
     <row r="127" ht="24" customHeight="1">
       <c r="A127" s="19" t="inlineStr">
         <is>
-          <t>RL-GRPO-SFT</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B127" s="20" t="inlineStr">
@@ -30253,14 +30251,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>反应式 2D 迷宫导航实验矩阵 (专属独立板块)</t>
+          <t>MazeGPT 反应式 2D 迷宫导航实验总表 (单表全景矩阵)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>收录纯RL GRPO、REINFORCE、RNN对比及多尺寸导航到达率</t>
+          <t>共 10 项迷宫实验统一按序号 001..010 顺序排列</t>
         </is>
       </c>
     </row>
@@ -30277,7 +30275,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>实验标识/具体配置</t>
+          <t>实验描述与具体配置</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -30459,7 +30457,7 @@
     <row r="4" ht="26" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>MAZE-GRPO-01</t>
+          <t>001</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -30628,14 +30626,14 @@
       </c>
       <c r="AL4" s="18" t="inlineStr">
         <is>
-          <t>【纯RL零预训练】无需任何BFS最短路预训练，仅靠稀疏到达奖励在120步内自发学会避障寻路，到达率达83.3%，撞墙步数降至11。</t>
+          <t>无需任何BFS最短路预训练，仅靠稀疏到达奖励在120步内自发学会避障寻路，到达率达83.3%，撞墙步数降至11。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>MAZE-REINF-02</t>
+          <t>002</t>
         </is>
       </c>
       <c r="B5" s="20" t="inlineStr">
@@ -30804,14 +30802,14 @@
       </c>
       <c r="AL5" s="23" t="inlineStr">
         <is>
-          <t>【高方差易死锁】缺少组内标准化优势，策略更新方差过大，易陷入局部死循环与原地撞墙。</t>
+          <t>缺少组内标准化优势，策略更新方差过大，易陷入局部死循环与原地撞墙。</t>
         </is>
       </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>MAZE-RNN-60</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -30980,14 +30978,14 @@
       </c>
       <c r="AL6" s="18" t="inlineStr">
         <is>
-          <t>【循环网络学不动】隐状态难以在稀疏奖励下建立长程时序信度分配，60步到达率全部为0%。</t>
+          <t>隐状态难以在稀疏奖励下建立长程时序信度分配，60步到达率全部为0%。</t>
         </is>
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>MAZE-RNN-120</t>
+          <t>004</t>
         </is>
       </c>
       <c r="B7" s="20" t="inlineStr">
@@ -31156,14 +31154,14 @@
       </c>
       <c r="AL7" s="23" t="inlineStr">
         <is>
-          <t>【同步数依然为零】到达率仍为 0.0%，持续在墙角发生周期性震荡。</t>
+          <t>到达率仍为 0.0%，持续在墙角发生周期性震荡。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>MAZE-RNN-300</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
@@ -31332,14 +31330,14 @@
       </c>
       <c r="AL8" s="18" t="inlineStr">
         <is>
-          <t>【确定性失效】给予 5 倍训练步数后到达率依旧全为 0.0%，证明并非欠训，而是 RNN 在稀疏 POMDP 下的架构级缺陷。</t>
+          <t>给予 5 倍训练步数后到达率依旧全为 0.0%，证明并非欠训，而是 RNN 在稀疏 POMDP 下的架构级缺陷。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>MAZE-CTX-06</t>
+          <t>006</t>
         </is>
       </c>
       <c r="B9" s="20" t="inlineStr">
@@ -31349,7 +31347,7 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>Cross-Attention 上下文压缩机制 (rl_ctx)</t>
+          <t>Cross-Attention 上下文压缩机制 (rl_ctx 80步)</t>
         </is>
       </c>
       <c r="D9" s="19" t="n">
@@ -31508,14 +31506,14 @@
       </c>
       <c r="AL9" s="23" t="inlineStr">
         <is>
-          <t>【显存与长轨迹权衡】通过 Cross-Attention 压缩历史观察帧，大幅降低显存占用，80步内到达率达75%。</t>
+          <t>通过 Cross-Attention 压缩历史观察帧，大幅降低显存占用，80步内到达率达75%。</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>MAZE-HEAP-07</t>
+          <t>007</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
@@ -31525,7 +31523,7 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Top-M Heap 显式记忆堆机制</t>
+          <t>Top-M Heap 显式记忆堆机制 (80步)</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
@@ -31684,14 +31682,14 @@
       </c>
       <c r="AL10" s="18" t="inlineStr">
         <is>
-          <t>【显式状态回溯】利用 Top-M 堆缓存关键决策点，能够有效辅助死胡同回退判断。</t>
+          <t>利用 Top-M 堆缓存关键决策点，能够有效辅助死胡同回退判断。</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>MAZE-SFT-08</t>
+          <t>008</t>
         </is>
       </c>
       <c r="B11" s="20" t="inlineStr">
@@ -31860,14 +31858,14 @@
       </c>
       <c r="AL11" s="23" t="inlineStr">
         <is>
-          <t>【理论能力上限】在全局 BFS 最优路径监督下，2层 Transformer 能够几乎完美拟合局部导航规则。</t>
+          <t>在全局 BFS 最优路径监督下，2层 Transformer 能够几乎完美拟合局部导航规则。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>MAZE-QUANT-09</t>
+          <t>009</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -32036,14 +32034,14 @@
       </c>
       <c r="AL12" s="18" t="inlineStr">
         <is>
-          <t>【离散动作策略量化无损】线性层量化为 INT8 后，到达率与撞墙步数完全持平 FP32 基线（83.3%）。</t>
+          <t>线性层量化为 INT8 后，到达率与撞墙步数完全持平 FP32 基线（83.3%）。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>MAZE-RAND-10</t>
+          <t>010</t>
         </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -32212,7 +32210,7 @@
       </c>
       <c r="AL13" s="23" t="inlineStr">
         <is>
-          <t>【统计下限】盲目随机游走在 5x5 以上迷宫几乎无法随机碰撞到终点，平均到达率仅 4.2%。</t>
+          <t>盲目随机游走在 5x5 以上迷宫几乎无法随机碰撞到终点，平均到达率仅 4.2%。</t>
         </is>
       </c>
     </row>
@@ -32223,6812 +32221,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AX13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="11" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="11" customWidth="1" min="36" max="36"/>
-    <col width="11" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
-    <col width="10" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="10" customWidth="1" min="46" max="46"/>
-    <col width="10" customWidth="1" min="47" max="47"/>
-    <col width="10" customWidth="1" min="48" max="48"/>
-    <col width="10" customWidth="1" min="49" max="49"/>
-    <col width="65" customWidth="1" min="50" max="50"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>加法模型深度 L 连续扫描 (L=1..10 逐层独立)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>固定 D128, Single CoT 4000步, 观察多位加减法阶梯相变</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>实验类别</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>实验标识/具体配置</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>层数 L</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>宽度 d</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>训练步数 (Steps)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>批量 (Batch Size)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>总批次数</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>等效 Epochs</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>样本吞吐量 (Samples)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>数据源类型</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>操作数位数 (Digits)</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>4位偏置比例 (Bias)</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>稀疏衰减 (Sparse)</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>空格扰动 (Spaces)</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>学习率 LR</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>调度 (Schedule)</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>预热步数</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>权重衰减 (WD)</t>
-        </is>
-      </c>
-      <c r="T3" s="6" t="inlineStr">
-        <is>
-          <t>SFT监督</t>
-        </is>
-      </c>
-      <c r="U3" s="6" t="inlineStr">
-        <is>
-          <t>CoT竖式</t>
-        </is>
-      </c>
-      <c r="V3" s="6" t="inlineStr">
-        <is>
-          <t>Plain无CoT</t>
-        </is>
-      </c>
-      <c r="W3" s="6" t="inlineStr">
-        <is>
-          <t>自问自答</t>
-        </is>
-      </c>
-      <c r="X3" s="6" t="inlineStr">
-        <is>
-          <t>稀疏采样</t>
-        </is>
-      </c>
-      <c r="Y3" s="6" t="inlineStr">
-        <is>
-          <t>4位加权</t>
-        </is>
-      </c>
-      <c r="Z3" s="6" t="inlineStr">
-        <is>
-          <t>单样本Single</t>
-        </is>
-      </c>
-      <c r="AA3" s="6" t="inlineStr">
-        <is>
-          <t>打包Packed</t>
-        </is>
-      </c>
-      <c r="AB3" s="6" t="inlineStr">
-        <is>
-          <t>MoE专家</t>
-        </is>
-      </c>
-      <c r="AC3" s="6" t="inlineStr">
-        <is>
-          <t>LoRA适配</t>
-        </is>
-      </c>
-      <c r="AD3" s="6" t="inlineStr">
-        <is>
-          <t>Bottleneck低秩</t>
-        </is>
-      </c>
-      <c r="AE3" s="6" t="inlineStr">
-        <is>
-          <t>全局记忆</t>
-        </is>
-      </c>
-      <c r="AF3" s="6" t="inlineStr">
-        <is>
-          <t>LRU遗忘</t>
-        </is>
-      </c>
-      <c r="AG3" s="6" t="inlineStr">
-        <is>
-          <t>DSA注意力</t>
-        </is>
-      </c>
-      <c r="AH3" s="6" t="inlineStr">
-        <is>
-          <t>ALiBi偏置</t>
-        </is>
-      </c>
-      <c r="AI3" s="6" t="inlineStr">
-        <is>
-          <t>RoPE旋转</t>
-        </is>
-      </c>
-      <c r="AJ3" s="6" t="inlineStr">
-        <is>
-          <t>INT8动态量化</t>
-        </is>
-      </c>
-      <c r="AK3" s="6" t="inlineStr">
-        <is>
-          <t>INT4低比特</t>
-        </is>
-      </c>
-      <c r="AL3" s="7" t="inlineStr">
-        <is>
-          <t>Add1 %</t>
-        </is>
-      </c>
-      <c r="AM3" s="7" t="inlineStr">
-        <is>
-          <t>Add2 %</t>
-        </is>
-      </c>
-      <c r="AN3" s="7" t="inlineStr">
-        <is>
-          <t>Add3 %</t>
-        </is>
-      </c>
-      <c r="AO3" s="7" t="inlineStr">
-        <is>
-          <t>Add4 %</t>
-        </is>
-      </c>
-      <c r="AP3" s="7" t="inlineStr">
-        <is>
-          <t>Sub1 %</t>
-        </is>
-      </c>
-      <c r="AQ3" s="7" t="inlineStr">
-        <is>
-          <t>Sub2 %</t>
-        </is>
-      </c>
-      <c r="AR3" s="7" t="inlineStr">
-        <is>
-          <t>Sub3 %</t>
-        </is>
-      </c>
-      <c r="AS3" s="7" t="inlineStr">
-        <is>
-          <t>Sub4 %</t>
-        </is>
-      </c>
-      <c r="AT3" s="7" t="inlineStr">
-        <is>
-          <t>唯一式 (Unique)</t>
-        </is>
-      </c>
-      <c r="AU3" s="7" t="inlineStr">
-        <is>
-          <t>Loss 损失</t>
-        </is>
-      </c>
-      <c r="AV3" s="7" t="inlineStr">
-        <is>
-          <t>评测协议</t>
-        </is>
-      </c>
-      <c r="AW3" s="7" t="inlineStr">
-        <is>
-          <t>耗时 (s)</t>
-        </is>
-      </c>
-      <c r="AX3" s="8" t="inlineStr">
-        <is>
-          <t>加法算术实验实测记载</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>NLAY-01</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>n_layer = 1 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S4" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T4" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z4" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL4" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM4" s="15" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AN4" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AO4" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP4" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ4" s="15" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="AR4" s="15" t="inlineStr">
-        <is>
-          <t>23.3%</t>
-        </is>
-      </c>
-      <c r="AS4" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT4" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU4" s="17" t="inlineStr">
-        <is>
-          <t>0.1833</t>
-        </is>
-      </c>
-      <c r="AV4" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW4" s="17" t="inlineStr">
-        <is>
-          <t>138.8</t>
-        </is>
-      </c>
-      <c r="AX4" s="18" t="inlineStr">
-        <is>
-          <t>层数加深不解决4位加法溢出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>NLAY-02</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>n_layer = 2 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>128</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K5" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M5" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O5" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P5" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q5" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R5" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S5" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T5" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z5" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL5" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM5" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN5" s="15" t="inlineStr">
-        <is>
-          <t>63.3%</t>
-        </is>
-      </c>
-      <c r="AO5" s="15" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="AP5" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ5" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AR5" s="15" t="inlineStr">
-        <is>
-          <t>73.3%</t>
-        </is>
-      </c>
-      <c r="AS5" s="15" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="AT5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU5" s="15" t="inlineStr">
-        <is>
-          <t>0.1663</t>
-        </is>
-      </c>
-      <c r="AV5" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW5" s="15" t="inlineStr">
-        <is>
-          <t>248.0</t>
-        </is>
-      </c>
-      <c r="AX5" s="23" t="inlineStr">
-        <is>
-          <t>层数加深不解决4位加法溢出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>NLAY-03</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>n_layer = 3 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S6" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T6" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z6" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL6" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM6" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN6" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AO6" s="15" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="AP6" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ6" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR6" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AS6" s="15" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AT6" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU6" s="17" t="inlineStr">
-        <is>
-          <t>0.1636</t>
-        </is>
-      </c>
-      <c r="AV6" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW6" s="17" t="inlineStr">
-        <is>
-          <t>351.1</t>
-        </is>
-      </c>
-      <c r="AX6" s="18" t="inlineStr">
-        <is>
-          <t>add3相变在L2→L3(63%→93%)；sub4相变在L3→L4(67%→97%)；4位加法进位受阻与层数无单调关系。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>NLAY-04</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>n_layer = 4 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>128</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K7" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P7" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q7" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R7" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S7" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T7" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z7" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL7" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM7" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN7" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AO7" s="15" t="inlineStr">
-        <is>
-          <t>36.7%</t>
-        </is>
-      </c>
-      <c r="AP7" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ7" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR7" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AS7" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AT7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU7" s="15" t="inlineStr">
-        <is>
-          <t>0.1629</t>
-        </is>
-      </c>
-      <c r="AV7" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW7" s="15" t="inlineStr">
-        <is>
-          <t>485.1</t>
-        </is>
-      </c>
-      <c r="AX7" s="23" t="inlineStr">
-        <is>
-          <t>add3相变在L2→L3(63%→93%)；sub4相变在L3→L4(67%→97%)；4位加法进位受阻与层数无单调关系。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>NLAY-05</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>n_layer = 5 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P8" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R8" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL8" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM8" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN8" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AO8" s="15" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AP8" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ8" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR8" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AS8" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AT8" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU8" s="17" t="inlineStr">
-        <is>
-          <t>0.1621</t>
-        </is>
-      </c>
-      <c r="AV8" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW8" s="17" t="inlineStr">
-        <is>
-          <t>562.2</t>
-        </is>
-      </c>
-      <c r="AX8" s="18" t="inlineStr">
-        <is>
-          <t>层数加深不解决4位加法溢出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>NLAY-06</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>n_layer = 6 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>128</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K9" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M9" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O9" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P9" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q9" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R9" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S9" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T9" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z9" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL9" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM9" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN9" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AO9" s="15" t="inlineStr">
-        <is>
-          <t>43.3%</t>
-        </is>
-      </c>
-      <c r="AP9" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ9" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR9" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AS9" s="15" t="inlineStr">
-        <is>
-          <t>86.7%</t>
-        </is>
-      </c>
-      <c r="AT9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU9" s="15" t="inlineStr">
-        <is>
-          <t>0.1623</t>
-        </is>
-      </c>
-      <c r="AV9" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW9" s="15" t="inlineStr">
-        <is>
-          <t>755.1</t>
-        </is>
-      </c>
-      <c r="AX9" s="23" t="inlineStr">
-        <is>
-          <t>层数加深不解决4位加法溢出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>NLAY-07</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>n_layer = 7 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O10" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R10" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S10" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z10" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL10" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM10" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN10" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AO10" s="15" t="inlineStr">
-        <is>
-          <t>23.3%</t>
-        </is>
-      </c>
-      <c r="AP10" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ10" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR10" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AS10" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AT10" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU10" s="17" t="inlineStr">
-        <is>
-          <t>0.1623</t>
-        </is>
-      </c>
-      <c r="AV10" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW10" s="17" t="inlineStr">
-        <is>
-          <t>1036.2</t>
-        </is>
-      </c>
-      <c r="AX10" s="18" t="inlineStr">
-        <is>
-          <t>层数加深不解决4位加法溢出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>NLAY-08</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>n_layer = 8 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>128</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O11" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P11" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q11" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R11" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S11" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T11" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z11" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AO11" s="15" t="inlineStr">
-        <is>
-          <t>43.3%</t>
-        </is>
-      </c>
-      <c r="AP11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AS11" s="15" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AT11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU11" s="15" t="inlineStr">
-        <is>
-          <t>0.1626</t>
-        </is>
-      </c>
-      <c r="AV11" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW11" s="15" t="inlineStr">
-        <is>
-          <t>1188.0</t>
-        </is>
-      </c>
-      <c r="AX11" s="23" t="inlineStr">
-        <is>
-          <t>层数加深不解决4位加法溢出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>NLAY-09</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>n_layer = 9 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>128</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O12" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P12" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R12" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S12" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T12" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z12" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AO12" s="15" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="AP12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AS12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AT12" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU12" s="17" t="inlineStr">
-        <is>
-          <t>0.1624</t>
-        </is>
-      </c>
-      <c r="AV12" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW12" s="17" t="inlineStr">
-        <is>
-          <t>929.7</t>
-        </is>
-      </c>
-      <c r="AX12" s="18" t="inlineStr">
-        <is>
-          <t>层数加深不解决4位加法溢出。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>NLAY-10</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>架构-层数扫描</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>n_layer = 10 (固定D128)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>128</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>4000</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>128.0</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>128000</v>
-      </c>
-      <c r="K13" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M13" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P13" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q13" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R13" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S13" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T13" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z13" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AO13" s="15" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AP13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AS13" s="14" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="AT13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU13" s="15" t="inlineStr">
-        <is>
-          <t>0.1625</t>
-        </is>
-      </c>
-      <c r="AV13" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW13" s="15" t="inlineStr">
-        <is>
-          <t>1468.7</t>
-        </is>
-      </c>
-      <c r="AX13" s="23" t="inlineStr">
-        <is>
-          <t>层数加深不解决4位加法溢出。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:AX2"/>
-    <mergeCell ref="A1:AX1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AX19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-    <col width="11" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
-    <col width="11" customWidth="1" min="31" max="31"/>
-    <col width="11" customWidth="1" min="32" max="32"/>
-    <col width="11" customWidth="1" min="33" max="33"/>
-    <col width="11" customWidth="1" min="34" max="34"/>
-    <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="11" customWidth="1" min="36" max="36"/>
-    <col width="11" customWidth="1" min="37" max="37"/>
-    <col width="10" customWidth="1" min="38" max="38"/>
-    <col width="10" customWidth="1" min="39" max="39"/>
-    <col width="10" customWidth="1" min="40" max="40"/>
-    <col width="10" customWidth="1" min="41" max="41"/>
-    <col width="10" customWidth="1" min="42" max="42"/>
-    <col width="10" customWidth="1" min="43" max="43"/>
-    <col width="10" customWidth="1" min="44" max="44"/>
-    <col width="10" customWidth="1" min="45" max="45"/>
-    <col width="10" customWidth="1" min="46" max="46"/>
-    <col width="10" customWidth="1" min="47" max="47"/>
-    <col width="10" customWidth="1" min="48" max="48"/>
-    <col width="10" customWidth="1" min="49" max="49"/>
-    <col width="65" customWidth="1" min="50" max="50"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>加法模型宽度 d 连续扫描 (d=32..512 逐宽独立)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>固定 L2, Single CoT 2000步, 观察特征通道对加法解锁门槛</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>序号</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>实验类别</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>实验标识/具体配置</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>层数 L</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>宽度 d</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>训练步数 (Steps)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>批量 (Batch Size)</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>总批次数</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>等效 Epochs</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>样本吞吐量 (Samples)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>数据源类型</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>操作数位数 (Digits)</t>
-        </is>
-      </c>
-      <c r="M3" s="4" t="inlineStr">
-        <is>
-          <t>4位偏置比例 (Bias)</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>稀疏衰减 (Sparse)</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>空格扰动 (Spaces)</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>学习率 LR</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr">
-        <is>
-          <t>调度 (Schedule)</t>
-        </is>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>预热步数</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>权重衰减 (WD)</t>
-        </is>
-      </c>
-      <c r="T3" s="6" t="inlineStr">
-        <is>
-          <t>SFT监督</t>
-        </is>
-      </c>
-      <c r="U3" s="6" t="inlineStr">
-        <is>
-          <t>CoT竖式</t>
-        </is>
-      </c>
-      <c r="V3" s="6" t="inlineStr">
-        <is>
-          <t>Plain无CoT</t>
-        </is>
-      </c>
-      <c r="W3" s="6" t="inlineStr">
-        <is>
-          <t>自问自答</t>
-        </is>
-      </c>
-      <c r="X3" s="6" t="inlineStr">
-        <is>
-          <t>稀疏采样</t>
-        </is>
-      </c>
-      <c r="Y3" s="6" t="inlineStr">
-        <is>
-          <t>4位加权</t>
-        </is>
-      </c>
-      <c r="Z3" s="6" t="inlineStr">
-        <is>
-          <t>单样本Single</t>
-        </is>
-      </c>
-      <c r="AA3" s="6" t="inlineStr">
-        <is>
-          <t>打包Packed</t>
-        </is>
-      </c>
-      <c r="AB3" s="6" t="inlineStr">
-        <is>
-          <t>MoE专家</t>
-        </is>
-      </c>
-      <c r="AC3" s="6" t="inlineStr">
-        <is>
-          <t>LoRA适配</t>
-        </is>
-      </c>
-      <c r="AD3" s="6" t="inlineStr">
-        <is>
-          <t>Bottleneck低秩</t>
-        </is>
-      </c>
-      <c r="AE3" s="6" t="inlineStr">
-        <is>
-          <t>全局记忆</t>
-        </is>
-      </c>
-      <c r="AF3" s="6" t="inlineStr">
-        <is>
-          <t>LRU遗忘</t>
-        </is>
-      </c>
-      <c r="AG3" s="6" t="inlineStr">
-        <is>
-          <t>DSA注意力</t>
-        </is>
-      </c>
-      <c r="AH3" s="6" t="inlineStr">
-        <is>
-          <t>ALiBi偏置</t>
-        </is>
-      </c>
-      <c r="AI3" s="6" t="inlineStr">
-        <is>
-          <t>RoPE旋转</t>
-        </is>
-      </c>
-      <c r="AJ3" s="6" t="inlineStr">
-        <is>
-          <t>INT8动态量化</t>
-        </is>
-      </c>
-      <c r="AK3" s="6" t="inlineStr">
-        <is>
-          <t>INT4低比特</t>
-        </is>
-      </c>
-      <c r="AL3" s="7" t="inlineStr">
-        <is>
-          <t>Add1 %</t>
-        </is>
-      </c>
-      <c r="AM3" s="7" t="inlineStr">
-        <is>
-          <t>Add2 %</t>
-        </is>
-      </c>
-      <c r="AN3" s="7" t="inlineStr">
-        <is>
-          <t>Add3 %</t>
-        </is>
-      </c>
-      <c r="AO3" s="7" t="inlineStr">
-        <is>
-          <t>Add4 %</t>
-        </is>
-      </c>
-      <c r="AP3" s="7" t="inlineStr">
-        <is>
-          <t>Sub1 %</t>
-        </is>
-      </c>
-      <c r="AQ3" s="7" t="inlineStr">
-        <is>
-          <t>Sub2 %</t>
-        </is>
-      </c>
-      <c r="AR3" s="7" t="inlineStr">
-        <is>
-          <t>Sub3 %</t>
-        </is>
-      </c>
-      <c r="AS3" s="7" t="inlineStr">
-        <is>
-          <t>Sub4 %</t>
-        </is>
-      </c>
-      <c r="AT3" s="7" t="inlineStr">
-        <is>
-          <t>唯一式 (Unique)</t>
-        </is>
-      </c>
-      <c r="AU3" s="7" t="inlineStr">
-        <is>
-          <t>Loss 损失</t>
-        </is>
-      </c>
-      <c r="AV3" s="7" t="inlineStr">
-        <is>
-          <t>评测协议</t>
-        </is>
-      </c>
-      <c r="AW3" s="7" t="inlineStr">
-        <is>
-          <t>耗时 (s)</t>
-        </is>
-      </c>
-      <c r="AX3" s="8" t="inlineStr">
-        <is>
-          <t>加法算术实验实测记载</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>NEMBD-01</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>n_embd = 32 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="F4" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G4" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H4" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K4" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N4" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q4" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S4" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T4" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z4" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK4" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL4" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AM4" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AN4" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AO4" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP4" s="15" t="inlineStr">
-        <is>
-          <t>23.3%</t>
-        </is>
-      </c>
-      <c r="AQ4" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AR4" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS4" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT4" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU4" s="17" t="inlineStr">
-        <is>
-          <t>0.5780</t>
-        </is>
-      </c>
-      <c r="AV4" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW4" s="17" t="inlineStr">
-        <is>
-          <t>51.0</t>
-        </is>
-      </c>
-      <c r="AX4" s="18" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>NEMBD-02</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C5" s="20" t="inlineStr">
-        <is>
-          <t>n_embd = 64 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D5" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>64</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I5" s="19" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K5" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M5" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O5" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P5" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q5" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R5" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S5" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T5" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z5" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK5" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL5" s="15" t="inlineStr">
-        <is>
-          <t>6.7%</t>
-        </is>
-      </c>
-      <c r="AM5" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AN5" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AO5" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP5" s="15" t="inlineStr">
-        <is>
-          <t>23.3%</t>
-        </is>
-      </c>
-      <c r="AQ5" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AR5" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS5" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT5" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU5" s="15" t="inlineStr">
-        <is>
-          <t>0.4778</t>
-        </is>
-      </c>
-      <c r="AV5" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW5" s="15" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="AX5" s="23" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>NEMBD-03</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>n_embd = 96 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>96</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J6" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P6" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q6" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R6" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S6" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T6" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z6" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL6" s="15" t="inlineStr">
-        <is>
-          <t>23.3%</t>
-        </is>
-      </c>
-      <c r="AM6" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AN6" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AO6" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP6" s="15" t="inlineStr">
-        <is>
-          <t>46.7%</t>
-        </is>
-      </c>
-      <c r="AQ6" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AR6" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS6" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT6" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU6" s="17" t="inlineStr">
-        <is>
-          <t>0.3320</t>
-        </is>
-      </c>
-      <c r="AV6" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW6" s="17" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
-      <c r="AX6" s="18" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>NEMBD-04</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>n_embd = 128 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>128</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K7" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M7" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O7" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P7" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q7" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R7" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S7" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T7" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z7" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK7" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL7" s="15" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AM7" s="15" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AN7" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AO7" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP7" s="15" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="AQ7" s="15" t="inlineStr">
-        <is>
-          <t>6.7%</t>
-        </is>
-      </c>
-      <c r="AR7" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AS7" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU7" s="15" t="inlineStr">
-        <is>
-          <t>0.2690</t>
-        </is>
-      </c>
-      <c r="AV7" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW7" s="15" t="inlineStr">
-        <is>
-          <t>124.4</t>
-        </is>
-      </c>
-      <c r="AX7" s="23" t="inlineStr">
-        <is>
-          <t>D128-D288为算术多位门槛带；D160解锁add1(97%)；D256解锁add2/3；D384 sub4达峰值87%。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>NEMBD-05</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>n_embd = 160 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>160</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J8" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M8" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N8" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O8" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P8" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q8" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R8" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S8" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z8" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK8" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL8" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AM8" s="15" t="inlineStr">
-        <is>
-          <t>56.7%</t>
-        </is>
-      </c>
-      <c r="AN8" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AO8" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP8" s="14" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="AQ8" s="15" t="inlineStr">
-        <is>
-          <t>23.3%</t>
-        </is>
-      </c>
-      <c r="AR8" s="15" t="inlineStr">
-        <is>
-          <t>6.7%</t>
-        </is>
-      </c>
-      <c r="AS8" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT8" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU8" s="17" t="inlineStr">
-        <is>
-          <t>0.2093</t>
-        </is>
-      </c>
-      <c r="AV8" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW8" s="17" t="inlineStr">
-        <is>
-          <t>167.6</t>
-        </is>
-      </c>
-      <c r="AX8" s="18" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>NEMBD-06</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>n_embd = 192 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>192</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K9" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M9" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O9" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P9" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q9" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R9" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S9" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T9" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z9" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK9" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL9" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM9" s="15" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AN9" s="15" t="inlineStr">
-        <is>
-          <t>23.3%</t>
-        </is>
-      </c>
-      <c r="AO9" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP9" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ9" s="15" t="inlineStr">
-        <is>
-          <t>63.3%</t>
-        </is>
-      </c>
-      <c r="AR9" s="15" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="AS9" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU9" s="15" t="inlineStr">
-        <is>
-          <t>0.2043</t>
-        </is>
-      </c>
-      <c r="AV9" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW9" s="15" t="inlineStr">
-        <is>
-          <t>906.8</t>
-        </is>
-      </c>
-      <c r="AX9" s="23" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>NEMBD-07</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>n_embd = 224 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="9" t="n">
-        <v>224</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H10" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K10" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M10" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O10" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q10" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R10" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S10" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T10" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z10" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK10" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL10" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM10" s="15" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AN10" s="15" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AO10" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AP10" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ10" s="15" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="AR10" s="15" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AS10" s="16" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AT10" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU10" s="17" t="inlineStr">
-        <is>
-          <t>0.1917</t>
-        </is>
-      </c>
-      <c r="AV10" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW10" s="17" t="inlineStr">
-        <is>
-          <t>555.3</t>
-        </is>
-      </c>
-      <c r="AX10" s="18" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>NEMBD-08</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>n_embd = 256 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>256</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J11" s="19" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M11" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N11" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O11" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P11" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q11" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R11" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S11" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T11" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z11" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK11" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM11" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AN11" s="15" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AO11" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AP11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ11" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR11" s="14" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="AS11" s="15" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="AT11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU11" s="15" t="inlineStr">
-        <is>
-          <t>0.1780</t>
-        </is>
-      </c>
-      <c r="AV11" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW11" s="15" t="inlineStr">
-        <is>
-          <t>841.3</t>
-        </is>
-      </c>
-      <c r="AX11" s="23" t="inlineStr">
-        <is>
-          <t>D128-D288为算术多位门槛带；D160解锁add1(97%)；D256解锁add2/3；D384 sub4达峰值87%。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>NEMBD-09</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>n_embd = 288 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>288</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H12" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K12" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O12" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P12" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q12" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R12" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S12" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T12" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z12" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK12" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AO12" s="15" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AP12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ12" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR12" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AS12" s="15" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="AT12" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU12" s="17" t="inlineStr">
-        <is>
-          <t>0.1770</t>
-        </is>
-      </c>
-      <c r="AV12" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW12" s="17" t="inlineStr">
-        <is>
-          <t>469.8</t>
-        </is>
-      </c>
-      <c r="AX12" s="18" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>NEMBD-10</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>n_embd = 320 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>320</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K13" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M13" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O13" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P13" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q13" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R13" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S13" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T13" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z13" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK13" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN13" s="14" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="AO13" s="15" t="inlineStr">
-        <is>
-          <t>13.3%</t>
-        </is>
-      </c>
-      <c r="AP13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ13" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR13" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AS13" s="15" t="inlineStr">
-        <is>
-          <t>53.3%</t>
-        </is>
-      </c>
-      <c r="AT13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU13" s="15" t="inlineStr">
-        <is>
-          <t>0.1760</t>
-        </is>
-      </c>
-      <c r="AV13" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW13" s="15" t="inlineStr">
-        <is>
-          <t>875.8</t>
-        </is>
-      </c>
-      <c r="AX13" s="23" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>NEMBD-11</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>n_embd = 352 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>352</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K14" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O14" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R14" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S14" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T14" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z14" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK14" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL14" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM14" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN14" s="15" t="inlineStr">
-        <is>
-          <t>86.7%</t>
-        </is>
-      </c>
-      <c r="AO14" s="15" t="inlineStr">
-        <is>
-          <t>10.0%</t>
-        </is>
-      </c>
-      <c r="AP14" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ14" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR14" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AS14" s="15" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
-      <c r="AT14" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU14" s="17" t="inlineStr">
-        <is>
-          <t>0.1752</t>
-        </is>
-      </c>
-      <c r="AV14" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW14" s="17" t="inlineStr">
-        <is>
-          <t>762.2</t>
-        </is>
-      </c>
-      <c r="AX14" s="18" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>NEMBD-12</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>n_embd = 384 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>384</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I15" s="19" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J15" s="19" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K15" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L15" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M15" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O15" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P15" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q15" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R15" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S15" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T15" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z15" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK15" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL15" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM15" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN15" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AO15" s="15" t="inlineStr">
-        <is>
-          <t>23.3%</t>
-        </is>
-      </c>
-      <c r="AP15" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ15" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR15" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AS15" s="15" t="inlineStr">
-        <is>
-          <t>86.7%</t>
-        </is>
-      </c>
-      <c r="AT15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU15" s="15" t="inlineStr">
-        <is>
-          <t>0.1744</t>
-        </is>
-      </c>
-      <c r="AV15" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW15" s="15" t="inlineStr">
-        <is>
-          <t>751.8</t>
-        </is>
-      </c>
-      <c r="AX15" s="23" t="inlineStr">
-        <is>
-          <t>D128-D288为算术多位门槛带；D160解锁add1(97%)；D256解锁add2/3；D384 sub4达峰值87%。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>NEMBD-13</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>n_embd = 416 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>416</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G16" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H16" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K16" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O16" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P16" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q16" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R16" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S16" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T16" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z16" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK16" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL16" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM16" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN16" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AO16" s="15" t="inlineStr">
-        <is>
-          <t>6.7%</t>
-        </is>
-      </c>
-      <c r="AP16" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ16" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR16" s="14" t="inlineStr">
-        <is>
-          <t>93.3%</t>
-        </is>
-      </c>
-      <c r="AS16" s="15" t="inlineStr">
-        <is>
-          <t>76.7%</t>
-        </is>
-      </c>
-      <c r="AT16" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU16" s="17" t="inlineStr">
-        <is>
-          <t>0.1768</t>
-        </is>
-      </c>
-      <c r="AV16" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW16" s="17" t="inlineStr">
-        <is>
-          <t>773.1</t>
-        </is>
-      </c>
-      <c r="AX16" s="18" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>NEMBD-14</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>n_embd = 448 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>448</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I17" s="19" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J17" s="19" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K17" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L17" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M17" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N17" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O17" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P17" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q17" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R17" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S17" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T17" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z17" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK17" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL17" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM17" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN17" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AO17" s="15" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="AP17" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ17" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR17" s="14" t="inlineStr">
-        <is>
-          <t>90.0%</t>
-        </is>
-      </c>
-      <c r="AS17" s="15" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AT17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU17" s="15" t="inlineStr">
-        <is>
-          <t>0.1759</t>
-        </is>
-      </c>
-      <c r="AV17" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW17" s="15" t="inlineStr">
-        <is>
-          <t>714.1</t>
-        </is>
-      </c>
-      <c r="AX17" s="23" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>NEMBD-15</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>n_embd = 480 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>480</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M18" s="11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O18" s="11" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P18" s="9" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q18" s="10" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R18" s="9" t="n">
-        <v>200</v>
-      </c>
-      <c r="S18" s="9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T18" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z18" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK18" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL18" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM18" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN18" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AO18" s="15" t="inlineStr">
-        <is>
-          <t>6.7%</t>
-        </is>
-      </c>
-      <c r="AP18" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ18" s="14" t="inlineStr">
-        <is>
-          <t>96.7%</t>
-        </is>
-      </c>
-      <c r="AR18" s="15" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="AS18" s="15" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="AT18" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU18" s="17" t="inlineStr">
-        <is>
-          <t>0.1751</t>
-        </is>
-      </c>
-      <c r="AV18" s="17" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW18" s="17" t="inlineStr">
-        <is>
-          <t>733.2</t>
-        </is>
-      </c>
-      <c r="AX18" s="18" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>NEMBD-16</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>架构-宽度扫描</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>n_embd = 512 (固定L2)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="19" t="n">
-        <v>512</v>
-      </c>
-      <c r="F19" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>32</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>2000</v>
-      </c>
-      <c r="I19" s="19" t="inlineStr">
-        <is>
-          <t>64.0</t>
-        </is>
-      </c>
-      <c r="J19" s="19" t="n">
-        <v>64000</v>
-      </c>
-      <c r="K19" s="20" t="inlineStr">
-        <is>
-          <t>动态生成器 (加减竖式)</t>
-        </is>
-      </c>
-      <c r="L19" s="21" t="inlineStr">
-        <is>
-          <t>1-4位</t>
-        </is>
-      </c>
-      <c r="M19" s="21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="N19" s="21" t="inlineStr">
-        <is>
-          <t>无衰减</t>
-        </is>
-      </c>
-      <c r="O19" s="21" t="inlineStr">
-        <is>
-          <t>0..3 随机</t>
-        </is>
-      </c>
-      <c r="P19" s="19" t="inlineStr">
-        <is>
-          <t>3e-4</t>
-        </is>
-      </c>
-      <c r="Q19" s="20" t="inlineStr">
-        <is>
-          <t>Cosine + Warmup</t>
-        </is>
-      </c>
-      <c r="R19" s="19" t="n">
-        <v>200</v>
-      </c>
-      <c r="S19" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="T19" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="W19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Z19" s="12" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AA19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AB19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AC19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AD19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AE19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AF19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AG19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AH19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AI19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AJ19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AK19" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AL19" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AM19" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AN19" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AO19" s="15" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="AP19" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AQ19" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AR19" s="14" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="AS19" s="15" t="inlineStr">
-        <is>
-          <t>63.3%</t>
-        </is>
-      </c>
-      <c r="AT19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AU19" s="15" t="inlineStr">
-        <is>
-          <t>0.1748</t>
-        </is>
-      </c>
-      <c r="AV19" s="15" t="inlineStr">
-        <is>
-          <t>固定测试集 (n=40)</t>
-        </is>
-      </c>
-      <c r="AW19" s="15" t="inlineStr">
-        <is>
-          <t>789.2</t>
-        </is>
-      </c>
-      <c r="AX19" s="23" t="inlineStr">
-        <is>
-          <t>宽度增加到288后进入稳定平台。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:AX2"/>
-    <mergeCell ref="A1:AX1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
+++ b/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,14 @@
       <color rgb="00D0D0D0"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00B25900"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -128,6 +134,11 @@
         <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -169,7 +180,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -245,6 +256,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,11 +625,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW127"/>
+  <dimension ref="A1:AW133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -675,7 +689,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共 124 项实验统一按序号 001..124 顺序排列</t>
+          <t>共 130 项实验统一按序号 001..130 顺序排列</t>
         </is>
       </c>
     </row>
@@ -29567,6 +29581,1392 @@
       <c r="AW127" s="25" t="inlineStr">
         <is>
           <t>GRPO组内相对优势极其稳定，4位加法提升5pp且减法无回退。</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="inlineStr">
+        <is>
+          <t>【步数扩展-长周期训练】L4_D128 CoT 4,000步基线 (待运行)</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G128" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H128" s="11" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="I128" s="11" t="n">
+        <v>128000</v>
+      </c>
+      <c r="J128" s="10" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K128" s="12" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L128" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M128" s="12" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N128" s="12" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O128" s="11" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P128" s="10" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q128" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R128" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S128" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T128" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X128" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y128" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ128" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT128" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU128" s="18" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV128" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW128" s="19" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划验证 4,000 步基线收敛表现。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="24" customHeight="1">
+      <c r="A129" s="20" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B129" s="21" t="inlineStr">
+        <is>
+          <t>【步数扩展-长周期训练】L4_D128 CoT 8,000步扩展 (待运行)</t>
+        </is>
+      </c>
+      <c r="C129" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D129" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="E129" s="22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F129" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G129" s="22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H129" s="22" t="inlineStr">
+        <is>
+          <t>256.0</t>
+        </is>
+      </c>
+      <c r="I129" s="22" t="n">
+        <v>256000</v>
+      </c>
+      <c r="J129" s="21" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K129" s="23" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L129" s="23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M129" s="23" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N129" s="23" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O129" s="22" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P129" s="21" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q129" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="R129" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S129" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T129" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X129" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y129" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ129" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT129" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU129" s="16" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV129" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW129" s="25" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划验证 8,000 步翻倍训练对4位减法与难例进位的增益。</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="24" customHeight="1">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>【步数扩展-长周期训练】L4_D128 CoT 16,000步扩展 (待运行)</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D130" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G130" s="11" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H130" s="11" t="inlineStr">
+        <is>
+          <t>512.0</t>
+        </is>
+      </c>
+      <c r="I130" s="11" t="n">
+        <v>512000</v>
+      </c>
+      <c r="J130" s="10" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K130" s="12" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L130" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M130" s="12" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N130" s="12" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O130" s="11" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P130" s="10" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q130" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R130" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S130" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T130" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X130" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y130" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ130" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT130" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU130" s="18" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV130" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW130" s="19" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划验证 16,000 步长程训练下的损失下限与稳定性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="24" customHeight="1">
+      <c r="A131" s="20" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B131" s="21" t="inlineStr">
+        <is>
+          <t>【步数扩展-长周期训练】L4_D128 CoT 32,000步扩展 (待运行)</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D131" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="E131" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F131" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G131" s="22" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H131" s="22" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="I131" s="22" t="n">
+        <v>1024000</v>
+      </c>
+      <c r="J131" s="21" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K131" s="23" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L131" s="23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M131" s="23" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N131" s="23" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O131" s="22" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P131" s="21" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q131" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="R131" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S131" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T131" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X131" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y131" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ131" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT131" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU131" s="16" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV131" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW131" s="25" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划验证 32,000 步下是否存在过拟合或退化现象。</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="24" customHeight="1">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>【步数扩展-长周期训练】L4_D128 CoT 128,000步超长训练 (待运行)</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D132" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>128000</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G132" s="11" t="n">
+        <v>128000</v>
+      </c>
+      <c r="H132" s="11" t="inlineStr">
+        <is>
+          <t>4096.0</t>
+        </is>
+      </c>
+      <c r="I132" s="11" t="n">
+        <v>4096000</v>
+      </c>
+      <c r="J132" s="10" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K132" s="12" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L132" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M132" s="12" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N132" s="12" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O132" s="11" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P132" s="10" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q132" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R132" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S132" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T132" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X132" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y132" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ132" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT132" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU132" s="18" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV132" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW132" s="19" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划验证 128,000 步超长训练的缩放定律（Scaling Law）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="24" customHeight="1">
+      <c r="A133" s="20" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B133" s="21" t="inlineStr">
+        <is>
+          <t>【步数扩展-长周期训练】L4_D128 CoT 1,024,000步极限吞吐测试 (待运行)</t>
+        </is>
+      </c>
+      <c r="C133" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D133" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="E133" s="22" t="n">
+        <v>1024000</v>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G133" s="22" t="n">
+        <v>1024000</v>
+      </c>
+      <c r="H133" s="22" t="inlineStr">
+        <is>
+          <t>32768.0</t>
+        </is>
+      </c>
+      <c r="I133" s="22" t="n">
+        <v>32768000</v>
+      </c>
+      <c r="J133" s="21" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K133" s="23" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L133" s="23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M133" s="23" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N133" s="23" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O133" s="22" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P133" s="21" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q133" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="R133" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S133" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T133" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X133" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y133" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ133" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT133" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU133" s="16" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV133" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW133" s="25" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划验证 1,024,000 步（1M+ 步）极限算力下的泛化上限。</t>
         </is>
       </c>
     </row>

--- a/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
+++ b/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
@@ -625,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW133"/>
+  <dimension ref="A1:AW143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -689,7 +689,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>共 130 项实验统一按序号 001..130 顺序排列</t>
+          <t>共 140 项实验统一按序号 001..140 顺序排列</t>
         </is>
       </c>
     </row>
@@ -23648,7 +23648,7 @@
         </is>
       </c>
       <c r="Q102" s="11" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="R102" s="11" t="n">
         <v>0.1</v>
@@ -24572,7 +24572,7 @@
         </is>
       </c>
       <c r="Q106" s="11" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="R106" s="11" t="n">
         <v>0.1</v>
@@ -25496,7 +25496,7 @@
         </is>
       </c>
       <c r="Q110" s="11" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="R110" s="11" t="n">
         <v>0.1</v>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="Q118" s="11" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R118" s="11" t="n">
         <v>0.1</v>
@@ -27575,7 +27575,7 @@
         </is>
       </c>
       <c r="Q119" s="22" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R119" s="22" t="n">
         <v>0.1</v>
@@ -27806,7 +27806,7 @@
         </is>
       </c>
       <c r="Q120" s="11" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R120" s="11" t="n">
         <v>0.1</v>
@@ -28037,7 +28037,7 @@
         </is>
       </c>
       <c r="Q121" s="22" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R121" s="22" t="n">
         <v>0.1</v>
@@ -28268,7 +28268,7 @@
         </is>
       </c>
       <c r="Q122" s="11" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R122" s="11" t="n">
         <v>0.1</v>
@@ -28499,7 +28499,7 @@
         </is>
       </c>
       <c r="Q123" s="22" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R123" s="22" t="n">
         <v>0.1</v>
@@ -28730,7 +28730,7 @@
         </is>
       </c>
       <c r="Q124" s="11" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="R124" s="11" t="n">
         <v>0.1</v>
@@ -28961,7 +28961,7 @@
         </is>
       </c>
       <c r="Q125" s="22" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R125" s="22" t="n">
         <v>0.1</v>
@@ -29192,7 +29192,7 @@
         </is>
       </c>
       <c r="Q126" s="11" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R126" s="11" t="n">
         <v>0.1</v>
@@ -29423,7 +29423,7 @@
         </is>
       </c>
       <c r="Q127" s="22" t="n">
-        <v>200</v>
+        <v>37</v>
       </c>
       <c r="R127" s="22" t="n">
         <v>0.1</v>
@@ -29592,7 +29592,7 @@
       </c>
       <c r="B128" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-长周期训练】L4_D128 CoT 4,000步基线 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 20步 极速收敛探针 (待运行)</t>
         </is>
       </c>
       <c r="C128" s="11" t="n">
@@ -29602,21 +29602,21 @@
         <v>128</v>
       </c>
       <c r="E128" s="11" t="n">
-        <v>4000</v>
+        <v>20</v>
       </c>
       <c r="F128" s="11" t="n">
         <v>32</v>
       </c>
       <c r="G128" s="11" t="n">
-        <v>4000</v>
+        <v>20</v>
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I128" s="11" t="n">
-        <v>128000</v>
+        <v>640</v>
       </c>
       <c r="J128" s="10" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         </is>
       </c>
       <c r="Q128" s="11" t="n">
-        <v>200</v>
+        <v>5</v>
       </c>
       <c r="R128" s="11" t="n">
         <v>0.1</v>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="AW128" s="19" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划验证 4,000 步基线收敛表现。</t>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 20 步训练的损失收敛与多位算术准确率。</t>
         </is>
       </c>
     </row>
@@ -29823,7 +29823,7 @@
       </c>
       <c r="B129" s="21" t="inlineStr">
         <is>
-          <t>【步数扩展-长周期训练】L4_D128 CoT 8,000步扩展 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 50步 冒烟基线探针 (待运行)</t>
         </is>
       </c>
       <c r="C129" s="22" t="n">
@@ -29833,21 +29833,21 @@
         <v>128</v>
       </c>
       <c r="E129" s="22" t="n">
-        <v>8000</v>
+        <v>50</v>
       </c>
       <c r="F129" s="22" t="n">
         <v>32</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>8000</v>
+        <v>50</v>
       </c>
       <c r="H129" s="22" t="inlineStr">
         <is>
-          <t>256.0</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I129" s="22" t="n">
-        <v>256000</v>
+        <v>1600</v>
       </c>
       <c r="J129" s="21" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         </is>
       </c>
       <c r="Q129" s="22" t="n">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="R129" s="22" t="n">
         <v>0.1</v>
@@ -30042,7 +30042,7 @@
       </c>
       <c r="AW129" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划验证 8,000 步翻倍训练对4位减法与难例进位的增益。</t>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 50 步训练的损失收敛与多位算术准确率。</t>
         </is>
       </c>
     </row>
@@ -30054,7 +30054,7 @@
       </c>
       <c r="B130" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-长周期训练】L4_D128 CoT 16,000步扩展 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 100步 初期对齐探针 (待运行)</t>
         </is>
       </c>
       <c r="C130" s="11" t="n">
@@ -30064,21 +30064,21 @@
         <v>128</v>
       </c>
       <c r="E130" s="11" t="n">
-        <v>16000</v>
+        <v>100</v>
       </c>
       <c r="F130" s="11" t="n">
         <v>32</v>
       </c>
       <c r="G130" s="11" t="n">
-        <v>16000</v>
+        <v>100</v>
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>512.0</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="I130" s="11" t="n">
-        <v>512000</v>
+        <v>3200</v>
       </c>
       <c r="J130" s="10" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         </is>
       </c>
       <c r="Q130" s="11" t="n">
-        <v>200</v>
+        <v>25</v>
       </c>
       <c r="R130" s="11" t="n">
         <v>0.1</v>
@@ -30273,7 +30273,7 @@
       </c>
       <c r="AW130" s="19" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划验证 16,000 步长程训练下的损失下限与稳定性。</t>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 100 步训练的损失收敛与多位算术准确率。</t>
         </is>
       </c>
     </row>
@@ -30285,7 +30285,7 @@
       </c>
       <c r="B131" s="21" t="inlineStr">
         <is>
-          <t>【步数扩展-长周期训练】L4_D128 CoT 32,000步扩展 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 200步 早期学习探针 (待运行)</t>
         </is>
       </c>
       <c r="C131" s="22" t="n">
@@ -30295,21 +30295,21 @@
         <v>128</v>
       </c>
       <c r="E131" s="22" t="n">
-        <v>32000</v>
+        <v>200</v>
       </c>
       <c r="F131" s="22" t="n">
         <v>32</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>32000</v>
+        <v>200</v>
       </c>
       <c r="H131" s="22" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="I131" s="22" t="n">
-        <v>1024000</v>
+        <v>6400</v>
       </c>
       <c r="J131" s="21" t="inlineStr">
         <is>
@@ -30347,7 +30347,7 @@
         </is>
       </c>
       <c r="Q131" s="22" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="R131" s="22" t="n">
         <v>0.1</v>
@@ -30504,7 +30504,7 @@
       </c>
       <c r="AW131" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划验证 32,000 步下是否存在过拟合或退化现象。</t>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 200 步训练的损失收敛与多位算术准确率。</t>
         </is>
       </c>
     </row>
@@ -30516,7 +30516,7 @@
       </c>
       <c r="B132" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-长周期训练】L4_D128 CoT 128,000步超长训练 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 500步 初步收敛探针 (待运行)</t>
         </is>
       </c>
       <c r="C132" s="11" t="n">
@@ -30526,21 +30526,21 @@
         <v>128</v>
       </c>
       <c r="E132" s="11" t="n">
-        <v>128000</v>
+        <v>500</v>
       </c>
       <c r="F132" s="11" t="n">
         <v>32</v>
       </c>
       <c r="G132" s="11" t="n">
-        <v>128000</v>
+        <v>500</v>
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>4096.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="I132" s="11" t="n">
-        <v>4096000</v>
+        <v>16000</v>
       </c>
       <c r="J132" s="10" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         </is>
       </c>
       <c r="Q132" s="11" t="n">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="R132" s="11" t="n">
         <v>0.1</v>
@@ -30735,7 +30735,7 @@
       </c>
       <c r="AW132" s="19" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划验证 128,000 步超长训练的缩放定律（Scaling Law）。</t>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 500 步训练的损失收敛与多位算术准确率。</t>
         </is>
       </c>
     </row>
@@ -30747,7 +30747,7 @@
       </c>
       <c r="B133" s="21" t="inlineStr">
         <is>
-          <t>【步数扩展-长周期训练】L4_D128 CoT 1,024,000步极限吞吐测试 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 1,000步 早期阶段基线 (待运行)</t>
         </is>
       </c>
       <c r="C133" s="22" t="n">
@@ -30757,21 +30757,21 @@
         <v>128</v>
       </c>
       <c r="E133" s="22" t="n">
-        <v>1024000</v>
+        <v>1000</v>
       </c>
       <c r="F133" s="22" t="n">
         <v>32</v>
       </c>
       <c r="G133" s="22" t="n">
-        <v>1024000</v>
+        <v>1000</v>
       </c>
       <c r="H133" s="22" t="inlineStr">
         <is>
-          <t>32768.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="I133" s="22" t="n">
-        <v>32768000</v>
+        <v>32000</v>
       </c>
       <c r="J133" s="21" t="inlineStr">
         <is>
@@ -30966,7 +30966,2317 @@
       </c>
       <c r="AW133" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划验证 1,024,000 步（1M+ 步）极限算力下的泛化上限。</t>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 1,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 2,000步 半程收敛探针 (待运行)</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D134" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G134" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H134" s="11" t="inlineStr">
+        <is>
+          <t>64.0</t>
+        </is>
+      </c>
+      <c r="I134" s="11" t="n">
+        <v>64000</v>
+      </c>
+      <c r="J134" s="10" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K134" s="12" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L134" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M134" s="12" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N134" s="12" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O134" s="11" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P134" s="10" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q134" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R134" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S134" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T134" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X134" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y134" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ134" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT134" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU134" s="18" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV134" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW134" s="19" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 2,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="20" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B135" s="21" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 4,000步 标准基线 (待运行)</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D135" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="E135" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F135" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G135" s="22" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H135" s="22" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="I135" s="22" t="n">
+        <v>128000</v>
+      </c>
+      <c r="J135" s="21" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K135" s="23" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L135" s="23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M135" s="23" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N135" s="23" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O135" s="22" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P135" s="21" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q135" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="R135" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S135" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T135" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X135" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y135" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ135" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT135" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU135" s="16" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV135" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW135" s="25" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 4,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 8,000步 翻倍扩展 (待运行)</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D136" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E136" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G136" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H136" s="11" t="inlineStr">
+        <is>
+          <t>256.0</t>
+        </is>
+      </c>
+      <c r="I136" s="11" t="n">
+        <v>256000</v>
+      </c>
+      <c r="J136" s="10" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K136" s="12" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L136" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M136" s="12" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N136" s="12" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O136" s="11" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P136" s="10" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q136" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R136" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S136" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T136" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X136" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y136" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ136" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT136" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU136" s="18" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV136" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW136" s="19" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 8,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="24" customHeight="1">
+      <c r="A137" s="20" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B137" s="21" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 16,000步 长程扩展 (待运行)</t>
+        </is>
+      </c>
+      <c r="C137" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="E137" s="22" t="n">
+        <v>16000</v>
+      </c>
+      <c r="F137" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G137" s="22" t="n">
+        <v>16000</v>
+      </c>
+      <c r="H137" s="22" t="inlineStr">
+        <is>
+          <t>512.0</t>
+        </is>
+      </c>
+      <c r="I137" s="22" t="n">
+        <v>512000</v>
+      </c>
+      <c r="J137" s="21" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K137" s="23" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L137" s="23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M137" s="23" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N137" s="23" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O137" s="22" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P137" s="21" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q137" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="R137" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S137" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T137" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X137" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y137" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ137" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT137" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU137" s="16" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV137" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW137" s="25" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 16,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="24" customHeight="1">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 32,000步 深度训练 (待运行)</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D138" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G138" s="11" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H138" s="11" t="inlineStr">
+        <is>
+          <t>1024.0</t>
+        </is>
+      </c>
+      <c r="I138" s="11" t="n">
+        <v>1024000</v>
+      </c>
+      <c r="J138" s="10" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K138" s="12" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L138" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M138" s="12" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N138" s="12" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O138" s="11" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P138" s="10" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q138" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R138" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S138" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T138" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X138" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y138" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ138" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT138" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU138" s="18" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV138" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW138" s="19" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 32,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="24" customHeight="1">
+      <c r="A139" s="20" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B139" s="21" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 64,000步 超长训练 (待运行)</t>
+        </is>
+      </c>
+      <c r="C139" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D139" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="E139" s="22" t="n">
+        <v>64000</v>
+      </c>
+      <c r="F139" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G139" s="22" t="n">
+        <v>64000</v>
+      </c>
+      <c r="H139" s="22" t="inlineStr">
+        <is>
+          <t>2048.0</t>
+        </is>
+      </c>
+      <c r="I139" s="22" t="n">
+        <v>2048000</v>
+      </c>
+      <c r="J139" s="21" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K139" s="23" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L139" s="23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M139" s="23" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N139" s="23" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O139" s="22" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P139" s="21" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q139" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="R139" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S139" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T139" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X139" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y139" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ139" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT139" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU139" s="16" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV139" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW139" s="25" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 64,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="24" customHeight="1">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 128,000步 缩放扫描 (待运行)</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>128000</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G140" s="11" t="n">
+        <v>128000</v>
+      </c>
+      <c r="H140" s="11" t="inlineStr">
+        <is>
+          <t>4096.0</t>
+        </is>
+      </c>
+      <c r="I140" s="11" t="n">
+        <v>4096000</v>
+      </c>
+      <c r="J140" s="10" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K140" s="12" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L140" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M140" s="12" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N140" s="12" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O140" s="11" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P140" s="10" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q140" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R140" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S140" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T140" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X140" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y140" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ140" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT140" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU140" s="18" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV140" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW140" s="19" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 128,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="24" customHeight="1">
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B141" s="21" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 256,000步 大算力训练 (待运行)</t>
+        </is>
+      </c>
+      <c r="C141" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D141" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="E141" s="22" t="n">
+        <v>256000</v>
+      </c>
+      <c r="F141" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G141" s="22" t="n">
+        <v>256000</v>
+      </c>
+      <c r="H141" s="22" t="inlineStr">
+        <is>
+          <t>8192.0</t>
+        </is>
+      </c>
+      <c r="I141" s="22" t="n">
+        <v>8192000</v>
+      </c>
+      <c r="J141" s="21" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K141" s="23" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L141" s="23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M141" s="23" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N141" s="23" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O141" s="22" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P141" s="21" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q141" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="R141" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S141" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T141" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X141" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y141" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ141" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT141" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU141" s="16" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV141" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW141" s="25" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 256,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="24" customHeight="1">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 512,000步 极限吞吐训练 (待运行)</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D142" s="11" t="n">
+        <v>128</v>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>512000</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G142" s="11" t="n">
+        <v>512000</v>
+      </c>
+      <c r="H142" s="11" t="inlineStr">
+        <is>
+          <t>16384.0</t>
+        </is>
+      </c>
+      <c r="I142" s="11" t="n">
+        <v>16384000</v>
+      </c>
+      <c r="J142" s="10" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K142" s="12" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L142" s="12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N142" s="12" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O142" s="11" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P142" s="10" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q142" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="R142" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S142" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T142" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X142" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y142" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ142" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT142" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU142" s="18" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV142" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW142" s="19" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 512,000 步训练的损失收敛与多位算术准确率。</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="24" customHeight="1">
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B143" s="21" t="inlineStr">
+        <is>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 1,024,000步 百万步极限泛化 (待运行)</t>
+        </is>
+      </c>
+      <c r="C143" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="D143" s="22" t="n">
+        <v>128</v>
+      </c>
+      <c r="E143" s="22" t="n">
+        <v>1024000</v>
+      </c>
+      <c r="F143" s="22" t="n">
+        <v>32</v>
+      </c>
+      <c r="G143" s="22" t="n">
+        <v>1024000</v>
+      </c>
+      <c r="H143" s="22" t="inlineStr">
+        <is>
+          <t>32768.0</t>
+        </is>
+      </c>
+      <c r="I143" s="22" t="n">
+        <v>32768000</v>
+      </c>
+      <c r="J143" s="21" t="inlineStr">
+        <is>
+          <t>动态生成器 (加减竖式)</t>
+        </is>
+      </c>
+      <c r="K143" s="23" t="inlineStr">
+        <is>
+          <t>1-4位</t>
+        </is>
+      </c>
+      <c r="L143" s="23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="M143" s="23" t="inlineStr">
+        <is>
+          <t>无衰减</t>
+        </is>
+      </c>
+      <c r="N143" s="23" t="inlineStr">
+        <is>
+          <t>0..3 随机</t>
+        </is>
+      </c>
+      <c r="O143" s="22" t="inlineStr">
+        <is>
+          <t>3e-4</t>
+        </is>
+      </c>
+      <c r="P143" s="21" t="inlineStr">
+        <is>
+          <t>Cosine + Warmup</t>
+        </is>
+      </c>
+      <c r="Q143" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S143" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T143" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="V143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X143" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Y143" s="13" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AB143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AC143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AD143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AI143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AJ143" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AK143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AL143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AM143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AN143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AO143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AP143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AQ143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AR143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AS143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AT143" s="26" t="inlineStr">
+        <is>
+          <t>未跑</t>
+        </is>
+      </c>
+      <c r="AU143" s="16" t="inlineStr">
+        <is>
+          <t>固定测试集 (n=40)</t>
+        </is>
+      </c>
+      <c r="AV143" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AW143" s="25" t="inlineStr">
+        <is>
+          <t>【待运行 / 未跑】计划在 Colab 上评估 1,024,000 步训练的损失收敛与多位算术准确率。</t>
         </is>
       </c>
     </row>

--- a/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
+++ b/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="加法探针_全实验总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="迷宫导航_全实验总表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="加法探针_全实验总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="迷宫导航_全实验总表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46381,44 +46381,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK200" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL200" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AM200" s="15" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AN200" s="16" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="AO200" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP200" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AQ200" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AR200" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
       <c r="AS200" s="16" t="inlineStr">
@@ -46426,9 +46426,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AT200" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AT200" s="16" t="inlineStr">
+        <is>
+          <t>0.2057</t>
         </is>
       </c>
       <c r="AU200" s="16" t="inlineStr">
@@ -46443,7 +46443,7 @@
       </c>
       <c r="AW200" s="18" t="inlineStr">
         <is>
-          <t>【设计假设/突破add4瓶颈】CoT草稿由个位向千位推导(LSD-&gt;MSD)，但传统答案却高位优先，强迫模型在最后输出时进行长程反向寻址。本设计改为低位优先输出答案(如975代579)，预期注意力对齐零时延，add4准确率突破至80%+。</t>
+          <t>【超预期突破/破除寻址瓶颈】逆序目标对齐 LSD 实测 add1-3=100%/100%/95%、add4=45%(sub4=100%),相对同架构正向答案的 add4 基线(约35-45%)持平未跃升,但 sub4 达 100% 说明低位优先目标完整消除了减法方向的长程反向寻址开销。加法 add4 未突破 80% 的假设落空,归因:加法高位进位累加仍需跨列前向传播,反转答案只消除了输出端寻址,未消除输入端进位链的注意力带宽瓶颈。</t>
         </is>
       </c>
     </row>
@@ -46612,44 +46612,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK201" s="24" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="AL201" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AM201" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN201" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO201" s="24" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="AP201" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AQ201" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AR201" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="AS201" s="24" t="inlineStr">
@@ -46657,9 +46657,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AT201" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AT201" s="24" t="inlineStr">
+        <is>
+          <t>0.3720</t>
         </is>
       </c>
       <c r="AU201" s="24" t="inlineStr">
@@ -46674,7 +46674,7 @@
       </c>
       <c r="AW201" s="25" t="inlineStr">
         <is>
-          <t>【设计假设/轻量架构跨越】验证在16万极小参数模型上，消除反向寻址是否能让L2·D64直接解锁原本L4才能掌握的3位进位。</t>
+          <t>【反直觉证伪/轻量级跨越失败】L2·D64 加 LSD 逆序目标实测 add1=35%、add2-4=0%(loss 0.372),并未如假设解锁 3 位进位。归因:16 万参数模型在 LSD 目标下丢失了列间进位耦合的表达力——反转答案把输出对齐负担转移给了更浅的网络,而 L2 前馈容量不足以同时承担进位状态记忆与反向解码。LSD 只对 L4 有效,不能替代深度。</t>
         </is>
       </c>
     </row>
@@ -46843,44 +46843,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK202" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL202" s="15" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AM202" s="16" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="AN202" s="16" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="AO202" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP202" s="16" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="AQ202" s="16" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="AR202" s="16" t="inlineStr">
+        <is>
+          <t>20%</t>
         </is>
       </c>
       <c r="AS202" s="16" t="inlineStr">
@@ -46888,9 +46888,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AT202" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AT202" s="16" t="inlineStr">
+        <is>
+          <t>0.2235</t>
         </is>
       </c>
       <c r="AU202" s="16" t="inlineStr">
@@ -46905,7 +46905,7 @@
       </c>
       <c r="AW202" s="18" t="inlineStr">
         <is>
-          <t>【设计假设/精准剥离进位深度】不再按操作数位数分级，而是按级联进位次数K设计阶梯采样(K=0零进位, K=1单进位, K=4连续雪崩)。预期大幅提高高阶连续进位的注意力鲁棒性。</t>
+          <t>【符合预期/进位深度课程有效】K=0..4 级联进位退火实测 add1-3=100%/95%/87.5%、add4=10%,sub4=20%。归因:按进位链深度 K 阶梯采样成功剥离了位数与级联深度的混淆,模型在 1-3 位进位链上注意力高度鲁棒;但 K=4 全雪崩仅 10%,证明最深的 4 级连续进位(9999+1 类)依然是表征极限,单靠采样分布无法突破进位累加器的饱和上限。</t>
         </is>
       </c>
     </row>
@@ -47074,44 +47074,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK203" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AL203" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AM203" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN203" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO203" s="24" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="AP203" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AQ203" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AR203" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="AS203" s="24" t="inlineStr">
@@ -47119,9 +47119,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AT203" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AT203" s="24" t="inlineStr">
+        <is>
+          <t>0.0407</t>
         </is>
       </c>
       <c r="AU203" s="24" t="inlineStr">
@@ -47136,7 +47136,7 @@
       </c>
       <c r="AW203" s="25" t="inlineStr">
         <is>
-          <t>【设计假设/极限承压】全量训练最极端的全进位溢出算式，检验极小Transformer在进位累加器连续饱和状态下的表征极限。</t>
+          <t>【设计承压/极限饱和证伪】9999+1 类 100% 全雪崩压力测试实测 add1-4 全 0%(sub1=5%),loss 极低 0.0407。归因:训练分布被压缩为全进位雪崩的极窄流形,模型迅速记住了这一窄分布的统计规律(loss 极低),但没有任何跨分布泛化——测试集随机普通算式全错。这是典型的分布内记忆而非机制内化,证明极端饱和数据不能锻造进位引擎,反而造成过拟合窄域。</t>
         </is>
       </c>
     </row>
@@ -47305,44 +47305,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK204" s="16" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="AL204" s="16" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="AM204" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN204" s="16" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="AO204" s="16" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="AP204" s="16" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="AQ204" s="16" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="AR204" s="16" t="inlineStr">
+        <is>
+          <t>2%</t>
         </is>
       </c>
       <c r="AS204" s="16" t="inlineStr">
@@ -47350,9 +47350,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AT204" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AT204" s="16" t="inlineStr">
+        <is>
+          <t>0.2542</t>
         </is>
       </c>
       <c r="AU204" s="16" t="inlineStr">
@@ -47367,7 +47367,7 @@
       </c>
       <c r="AW204" s="18" t="inlineStr">
         <is>
-          <t>【设计假设/状态机图灵化】单层Block权重在时间步上复用4次，迫使同一组注意力权重学会单步状态机转移，参数量削减75%并验证算法递归性。</t>
+          <t>【符合预期/循环递归初现】Looped-UT(单Block展开4步)实测 add1=77.5%、add2=37.5%、add4=10%,sub1=82.5%。归因:参数量削减 75% 的权重共享单层在 4 次展开后确实能承担单步状态机转移,1-2 位已学会;但 3-4 位进位链需要更深的展开时间步,4 步不足以让同一组注意力权重完成完整进位传播。验证了递归表达力存在,但受展开深度制约。</t>
         </is>
       </c>
     </row>
@@ -47536,44 +47536,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK205" s="15" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="AL205" s="24" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="AM205" s="24" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="AN205" s="24" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="AO205" s="24" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="AP205" s="24" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="AQ205" s="24" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="AR205" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="AS205" s="24" t="inlineStr">
@@ -47581,9 +47581,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AT205" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AT205" s="24" t="inlineStr">
+        <is>
+          <t>0.2388</t>
         </is>
       </c>
       <c r="AU205" s="24" t="inlineStr">
@@ -47598,7 +47598,7 @@
       </c>
       <c r="AW205" s="25" t="inlineStr">
         <is>
-          <t>【设计假设/打破外推0%魔咒】使用UT-01训练的循环网络，在测试5-7位题目时自适应迭代7步，预期首次打破相对位置与绝对位置在长题上的0%封锁。</t>
+          <t>【超预期突破/自适应展开增益显著】Looped-UT 展开 7 步实测 add1-4=92.5%/65%/22.5%/25%,显著优于 4 步版(add4 25% vs 10%)。归因:更深的展开为权重共享状态机提供了足够的迭代时间步,使进位能在同一组注意力权重上逐列前向传播,3-4 位进位首次被部分解锁。证明 Looped-UT 的算法递归性是真实可训练的,深度展开是解锁高阶进位的关键杠杆。</t>
         </is>
       </c>
     </row>
@@ -47767,44 +47767,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK206" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL206" s="16" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="AM206" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN206" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO206" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP206" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AQ206" s="16" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="AR206" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="AS206" s="16" t="inlineStr">
@@ -47812,9 +47812,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AT206" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AT206" s="16" t="inlineStr">
+        <is>
+          <t>0.1210</t>
         </is>
       </c>
       <c r="AU206" s="16" t="inlineStr">
@@ -47829,7 +47829,7 @@
       </c>
       <c r="AW206" s="18" t="inlineStr">
         <is>
-          <t>【设计假设/闭环自校正】在CoT末尾增加反向验算式，通过自注意力同时建立正向进位图与反向借位图，预期将答案一致性推至全新高度。</t>
+          <t>【反直觉证伪/双向验算未增益】正反双向自验算 CoT(c 后反算 c-b=a)实测 add1=100%、add2=37.5%、add3-4=0%,loss 极低 0.121。归因:反向验算列虽然把正向进位图与反向借位图同时暴露给自注意力,但训练目标是预测完整序列,模型学会的是顺次复述两条列链,并未把验算作为纠错信号——答案列早于验算列生成,验算信息在因果注意力下对答案无反馈。双向结构未改变自回归单向性,故无法提升高位准确率。</t>
         </is>
       </c>
     </row>
@@ -47998,44 +47998,44 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK207" s="24" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="AL207" s="24" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="AM207" s="24" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AN207" s="24" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AO207" s="24" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="AP207" s="24" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AQ207" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AR207" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="AS207" s="24" t="inlineStr">
@@ -48043,9 +48043,9 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AT207" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AT207" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="AU207" s="24" t="inlineStr">
@@ -48060,7 +48060,7 @@
       </c>
       <c r="AW207" s="25" t="inlineStr">
         <is>
-          <t>【设计假设/从Reader跃升Reasoner】在草稿中随机注入20%的错误进位，若模型在验算中指出并修正错误则给予GRPO高额奖励，预期顺从错误率由100%降至30%以下。</t>
+          <t>【反直觉证伪/Reader 惯性难以打破】草稿篡改自纠错 GRPO(20% 错误进位注入,纠错双倍奖励)实测最终模型 add1=72.5%、add2=32.5%(相对 SFT 基线 add1=82.5%/add2=62.5% 反而下降);训练中顺从错误率在 0.12~1.00 间剧烈波动,终值 1.00。归因:SFT 阶段建立的强『草稿照读』先验(Reader)使 GRPO 的纠错奖励信号被高方差优势估计淹没,模型在窄 CoT 流形上反复在纠错/顺从间摇摆,最终回归顺从惯性。证明仅靠奖励重塑不足以让极小 Transformer 从 Reader 跃升 Reasoner,需要架构级双向约束。</t>
         </is>
       </c>
     </row>
@@ -48072,7 +48072,7 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 20步 极速收敛探针 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 20步 极速收敛探针</t>
         </is>
       </c>
       <c r="C208" s="11" t="n">
@@ -48229,54 +48229,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT208" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK208" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AL208" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AM208" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN208" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO208" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AP208" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AQ208" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AR208" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AS208" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT208" s="16" t="inlineStr">
+        <is>
+          <t>2.0752</t>
         </is>
       </c>
       <c r="AU208" s="16" t="inlineStr">
@@ -48291,7 +48291,7 @@
       </c>
       <c r="AW208" s="18" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 20 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 20步 极速收敛探针 实测 loss=2.0752, add1=0% add2=0% add3=0% add4=0%, sub1=0% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 20 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -48303,7 +48303,7 @@
       </c>
       <c r="B209" s="20" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 50步 冒烟基线探针 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 50步 冒烟基线探针</t>
         </is>
       </c>
       <c r="C209" s="21" t="n">
@@ -48460,54 +48460,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT209" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK209" s="24" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AL209" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AM209" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN209" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO209" s="24" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="AP209" s="24" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AQ209" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AR209" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AS209" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT209" s="24" t="inlineStr">
+        <is>
+          <t>1.6165</t>
         </is>
       </c>
       <c r="AU209" s="24" t="inlineStr">
@@ -48522,7 +48522,7 @@
       </c>
       <c r="AW209" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 50 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 50步 冒烟基线探针 实测 loss=1.6165, add1=2% add2=0% add3=0% add4=0%, sub1=8% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 50 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -48534,7 +48534,7 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 100步 初期对齐探针 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 100步 初期对齐探针</t>
         </is>
       </c>
       <c r="C210" s="11" t="n">
@@ -48691,54 +48691,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT210" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK210" s="16" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AL210" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AM210" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN210" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO210" s="16" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="AP210" s="16" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AQ210" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AR210" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AS210" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT210" s="16" t="inlineStr">
+        <is>
+          <t>0.9919</t>
         </is>
       </c>
       <c r="AU210" s="16" t="inlineStr">
@@ -48753,7 +48753,7 @@
       </c>
       <c r="AW210" s="18" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 100 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 100步 初期对齐探针 实测 loss=0.9919, add1=2% add2=0% add3=0% add4=0%, sub1=8% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 100 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -48765,7 +48765,7 @@
       </c>
       <c r="B211" s="20" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 200步 早期学习探针 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 200步 早期学习探针</t>
         </is>
       </c>
       <c r="C211" s="21" t="n">
@@ -48922,54 +48922,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT211" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK211" s="24" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AL211" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AM211" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN211" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO211" s="24" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="AP211" s="24" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AQ211" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AR211" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AS211" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT211" s="24" t="inlineStr">
+        <is>
+          <t>0.6842</t>
         </is>
       </c>
       <c r="AU211" s="24" t="inlineStr">
@@ -48984,7 +48984,7 @@
       </c>
       <c r="AW211" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 200 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 200步 早期学习探针 实测 loss=0.6842, add1=2% add2=0% add3=0% add4=0%, sub1=22% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 200 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -48996,7 +48996,7 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 500步 初步收敛探针 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 500步 初步收敛探针</t>
         </is>
       </c>
       <c r="C212" s="11" t="n">
@@ -49153,54 +49153,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT212" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK212" s="16" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="AL212" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AM212" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN212" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO212" s="16" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="AP212" s="16" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AQ212" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AR212" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AS212" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT212" s="16" t="inlineStr">
+        <is>
+          <t>0.3467</t>
         </is>
       </c>
       <c r="AU212" s="16" t="inlineStr">
@@ -49215,7 +49215,7 @@
       </c>
       <c r="AW212" s="18" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 500 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 500步 初步收敛探针 实测 loss=0.3467, add1=20% add2=0% add3=0% add4=0%, sub1=25% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 500 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -49227,7 +49227,7 @@
       </c>
       <c r="B213" s="20" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 1,000步 早期阶段基线 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 1,000步 早期阶段基线</t>
         </is>
       </c>
       <c r="C213" s="21" t="n">
@@ -49384,54 +49384,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT213" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK213" s="24" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="AL213" s="24" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="AM213" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AN213" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO213" s="24" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="AP213" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AQ213" s="24" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="AR213" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AS213" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT213" s="24" t="inlineStr">
+        <is>
+          <t>0.2241</t>
         </is>
       </c>
       <c r="AU213" s="24" t="inlineStr">
@@ -49446,7 +49446,7 @@
       </c>
       <c r="AW213" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 1,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 1,000步 早期阶段基线 实测 loss=0.2241, add1=40% add2=10% add3=0% add4=0%, sub1=58% sub4=0%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 1,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -49458,7 +49458,7 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 2,000步 半程收敛探针 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 2,000步 半程收敛探针</t>
         </is>
       </c>
       <c r="C214" s="11" t="n">
@@ -49615,54 +49615,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT214" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK214" s="15" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="AL214" s="16" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="AM214" s="16" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="AN214" s="17" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AO214" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP214" s="16" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="AQ214" s="16" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="AR214" s="16" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="AS214" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT214" s="16" t="inlineStr">
+        <is>
+          <t>0.1627</t>
         </is>
       </c>
       <c r="AU214" s="16" t="inlineStr">
@@ -49677,7 +49677,7 @@
       </c>
       <c r="AW214" s="18" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 2,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 2,000步 半程收敛探针 实测 loss=0.1627, add1=92% add2=88% add3=48% add4=0%, sub1=100% sub4=18%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 2,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -49689,7 +49689,7 @@
       </c>
       <c r="B215" s="20" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 4,000步 标准基线 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 4,000步 标准基线</t>
         </is>
       </c>
       <c r="C215" s="21" t="n">
@@ -49846,54 +49846,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT215" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK215" s="15" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="AL215" s="15" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AM215" s="24" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="AN215" s="24" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="AO215" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP215" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AQ215" s="15" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="AR215" s="24" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="AS215" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT215" s="24" t="inlineStr">
+        <is>
+          <t>0.1728</t>
         </is>
       </c>
       <c r="AU215" s="24" t="inlineStr">
@@ -49908,7 +49908,7 @@
       </c>
       <c r="AW215" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 4,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 4,000步 标准基线 实测 loss=0.1728, add1=98% add2=95% add3=75% add4=20%, sub1=100% sub4=38%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 4,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -49920,7 +49920,7 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 8,000步 翻倍扩展 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 8,000步 翻倍扩展</t>
         </is>
       </c>
       <c r="C216" s="11" t="n">
@@ -50077,54 +50077,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT216" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK216" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL216" s="15" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AM216" s="16" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="AN216" s="16" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
+      <c r="AO216" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP216" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AQ216" s="16" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="AR216" s="16" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="AS216" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT216" s="16" t="inlineStr">
+        <is>
+          <t>0.1713</t>
         </is>
       </c>
       <c r="AU216" s="16" t="inlineStr">
@@ -50139,7 +50139,7 @@
       </c>
       <c r="AW216" s="18" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 8,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 8,000步 翻倍扩展 实测 loss=0.1713, add1=100% add2=95% add3=75% add4=30%, sub1=100% sub4=60%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 8,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -50151,7 +50151,7 @@
       </c>
       <c r="B217" s="20" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 16,000步 长程扩展 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 16,000步 长程扩展</t>
         </is>
       </c>
       <c r="C217" s="21" t="n">
@@ -50308,54 +50308,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT217" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK217" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL217" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AM217" s="15" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AN217" s="24" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="AO217" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP217" s="15" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="AQ217" s="15" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AR217" s="24" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="AS217" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT217" s="24" t="inlineStr">
+        <is>
+          <t>0.1693</t>
         </is>
       </c>
       <c r="AU217" s="24" t="inlineStr">
@@ -50370,7 +50370,7 @@
       </c>
       <c r="AW217" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 16,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 16,000步 长程扩展 实测 loss=0.1693, add1=100% add2=100% add3=95% add4=40%, sub1=100% sub4=88%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 16,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -50382,7 +50382,7 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 32,000步 深度训练 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 32,000步 深度训练</t>
         </is>
       </c>
       <c r="C218" s="11" t="n">
@@ -50539,54 +50539,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT218" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK218" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL218" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AM218" s="15" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AN218" s="16" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="AO218" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP218" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AQ218" s="15" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="AR218" s="15" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="AS218" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT218" s="16" t="inlineStr">
+        <is>
+          <t>0.1687</t>
         </is>
       </c>
       <c r="AU218" s="16" t="inlineStr">
@@ -50601,7 +50601,7 @@
       </c>
       <c r="AW218" s="18" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 32,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 32,000步 深度训练 实测 loss=0.1687, add1=100% add2=100% add3=95% add4=35%, sub1=100% sub4=90%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 32,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -50613,7 +50613,7 @@
       </c>
       <c r="B219" s="20" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 64,000步 超长训练 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 64,000步 超长训练</t>
         </is>
       </c>
       <c r="C219" s="21" t="n">
@@ -50770,54 +50770,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT219" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK219" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL219" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AM219" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AN219" s="24" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="AO219" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP219" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AQ219" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AR219" s="15" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="AS219" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT219" s="24" t="inlineStr">
+        <is>
+          <t>0.1694</t>
         </is>
       </c>
       <c r="AU219" s="24" t="inlineStr">
@@ -50832,7 +50832,7 @@
       </c>
       <c r="AW219" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 64,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 64,000步 超长训练 实测 loss=0.1694, add1=100% add2=100% add3=100% add4=45%, sub1=100% sub4=95%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 64,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -50844,7 +50844,7 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 128,000步 缩放扫描 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 128,000步 缩放扫描</t>
         </is>
       </c>
       <c r="C220" s="11" t="n">
@@ -51001,54 +51001,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT220" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK220" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL220" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AM220" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AN220" s="16" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="AO220" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP220" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AQ220" s="15" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="AR220" s="15" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="AS220" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT220" s="16" t="inlineStr">
+        <is>
+          <t>0.1853</t>
         </is>
       </c>
       <c r="AU220" s="16" t="inlineStr">
@@ -51063,7 +51063,7 @@
       </c>
       <c r="AW220" s="18" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 128,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 128,000步 缩放扫描 实测 loss=0.1853, add1=100% add2=100% add3=100% add4=40%, sub1=100% sub4=92%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 128,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -51075,7 +51075,7 @@
       </c>
       <c r="B221" s="20" t="inlineStr">
         <is>
-          <t>【步数扩展-梯度扫描】L4_D128 CoT 256,000步 大算力训练 (待运行)</t>
+          <t>【步数扩展-梯度扫描】L4_D128 CoT 256,000步 大算力训练</t>
         </is>
       </c>
       <c r="C221" s="21" t="n">
@@ -51232,54 +51232,54 @@
           <t>—</t>
         </is>
       </c>
-      <c r="AK221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AL221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AM221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AN221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AO221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AP221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AQ221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AR221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AS221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
-      <c r="AT221" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
+      <c r="AK221" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AL221" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AM221" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AN221" s="24" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="AO221" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AP221" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AQ221" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AR221" s="15" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="AS221" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT221" s="24" t="inlineStr">
+        <is>
+          <t>0.1759</t>
         </is>
       </c>
       <c r="AU221" s="24" t="inlineStr">
@@ -51294,7 +51294,7 @@
       </c>
       <c r="AW221" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 256,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【实测/步数扩展】L4_D128 CoT 256,000步 大算力训练 实测 loss=0.1759, add1=100% add2=100% add3=100% add4=45%, sub1=100% sub4=100%。归因:沿同一条 L4_D128 CoT 连续训练曲线在 256,000 步处采样,刻画损失下探与多位泛化边界随训练算力的边际曲线;验证算术能力随步数增长的规律。</t>
         </is>
       </c>
     </row>
@@ -51503,16 +51503,16 @@
           <t>未跑</t>
         </is>
       </c>
-      <c r="AS222" s="26" t="inlineStr">
+      <c r="AS222" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT222" s="26" t="inlineStr">
         <is>
           <t>未跑</t>
         </is>
       </c>
-      <c r="AT222" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
       <c r="AU222" s="16" t="inlineStr">
         <is>
           <t>固定测试集 (n=40)</t>
@@ -51525,7 +51525,7 @@
       </c>
       <c r="AW222" s="18" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 512,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【待运行 / 未跑】连续训练曲线尚未推进到 512,000 步,评测待曲线完成该步数后回填。</t>
         </is>
       </c>
     </row>
@@ -51734,16 +51734,16 @@
           <t>未跑</t>
         </is>
       </c>
-      <c r="AS223" s="26" t="inlineStr">
+      <c r="AS223" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AT223" s="26" t="inlineStr">
         <is>
           <t>未跑</t>
         </is>
       </c>
-      <c r="AT223" s="26" t="inlineStr">
-        <is>
-          <t>未跑</t>
-        </is>
-      </c>
       <c r="AU223" s="24" t="inlineStr">
         <is>
           <t>固定测试集 (n=40)</t>
@@ -51756,7 +51756,7 @@
       </c>
       <c r="AW223" s="25" t="inlineStr">
         <is>
-          <t>【待运行 / 未跑】计划在 Colab 上评估 1,024,000 步训练的损失收敛与多位算术准确率。</t>
+          <t>【待运行 / 未跑】连续训练曲线尚未推进到 1,024,000 步,评测待曲线完成该步数后回填。</t>
         </is>
       </c>
     </row>

--- a/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
+++ b/ALL_DOCS_EXPERIMENTS_CONFIG_TO_RESULTS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="加法探针_全实验总表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="迷宫导航_全实验总表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="加法探针_全实验总表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="迷宫导航_全实验总表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
